--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -14,6 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_介護保険外の住まいとの突合" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_調査の未回答と点検事項の解消" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_計画本文への反映と残る確認事項" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_指定事業所一覧と見える化の事業所数の突合" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_通常の事業の実施地域" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_特別養護老人ホームの定員" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -171,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,6 +248,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -631,7 +640,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>北海道が公表する5つの名簿（令和8年7月1日現在・サービス付き高齢者向け住宅のみ令和8年6月30日現在）から区域内の施設・住まいを抽出し、居所変更実態調査の施設等票18件及び見える化システムのK系列（事業所数）と突合した。調査だけでは把握できていなかった施設が明らかになったため、計画本文に載せる供給量の数値が変わる。作成日：令和8年8月4日。</t>
+          <t>北海道が公表する8つの名簿・データ（令和8年6月30日〜7月1日現在）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査の施設等票18件及び見える化システムのK系列（事業所数）と突合した。調査だけでは把握できていなかった施設が明らかになったため、計画本文に載せる供給量の数値が変わる。作成日：令和8年8月4日。</t>
         </is>
       </c>
     </row>
@@ -862,157 +871,351 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="13" ht="100" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホームの定員が確定した（160人＋62人）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム名簿により、介護老人福祉施設は3施設・定員160人（アゼリアハイツ50・東川町羽衣園50・美瑛慈光園60）、地域密着型介護老人福祉施設は3施設・定員62人（アゼリアハイツ ユニット型20・地域密着型美瑛慈光園24・サテライト特養燈18）である。見える化K1a・K1bの各3事業所と一致する。居所変更実態調査には東神楽町のアゼリアハイツが回答していない。</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>施設サービスの区域内定員を392人から462人に改める。定員160人は、資料依頼No.6③の「介護老人福祉施設の定員減少234人→160人」の160人と一致し、現在の定員が160人であることが裏付けられた。</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>通常の事業の実施地域が全事業所で判明した</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧（47区分）に運営規程の「通常の事業実施地域」が収録されている。区域内の指定事業所124件を抽出した。訪問介護13事業所のうち美瑛町を実施地域とするのは4事業所、東川町は5事業所、東神楽町は6事業所である。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>第1章第7節（訪問・通所困難地域）の唯一の客観的根拠であり、資料依頼No.10・確認No.15が解消した。第10期基本指針案の別表 一への対応が推量でなくなる。</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="100" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能5事業所はすべて社会福祉法人美瑛慈光会である</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>区域内の小規模多機能型居宅介護5事業所（虹・七彩・燈・ひなた・ほたる）は、すべて社会福祉法人美瑛慈光会により美瑛町で運営されている。東川町・東神楽町を実施地域とするのは「七彩」1事業所のみである。</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>点検事項No.2（同一法人の小規模多機能2事業所が利用者票の36票を占め、回答が「小規模多機能がより適切」に偏っている）の構造的な背景が明らかになった。区域内の小規模多機能がすべて1法人であるため、利用者票の偏りは調査設計の問題ではなく供給構造の反映である。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>グループホームは5事業所ではなく7事業所である</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧（令和8年6月30日現在）では認知症対応型共同生活介護が7事業所である。見える化K2c（令和6年度）は5事業所であり、グループホームファミリー（東川町）とグループホームくるみの郷（東川町）が新たに加わっている。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>居住系の定員がさらに増える可能性がある。2事業所の定員が不明であるため、介護サービス情報公表システム又は広域連合の台帳により確認する。居住系の見込量145人に対する定員の余裕はさらに大きくなる。</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="100" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>事業所数は見える化K系列と13区分中10区分で一致した</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>北海道の名簿から区域内を抽出した事業所数は、見える化K系列の事業所数と13区分のうち10区分で一致した。差があるのは認知症対応型共同生活介護（＋2）、居宅介護支援（＋3）、訪問リハビリテーション（▲1）である。</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>見える化のK系列を区域内の事業所数として用いてよいことが裏付けられた。訪問介護13事業所という母数が確定し、点検事項No.23（訪問系3事業所からの回答）の回収率が23.1％であることが確定した。</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>【供給量の新旧】</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>これまで（調査による）</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>今回（公表名簿による）</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>差</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>特定施設（介護付有料）</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>2施設・58人</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>3施設・156人</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>特定施設一覧・K2a</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>住宅型有料老人ホーム</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>3施設・91人</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>9施設・223人</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>届出済有料老人ホーム一覧</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>サービス付き高齢者向け住宅</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>1件・30戸</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>2件・66戸</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>住所地特例適用施設一覧</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>軽費老人ホーム（ケアハウス）</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>1施設・50人</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>軽費老人ホーム名簿</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>養護老人ホーム</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>区域内になし</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>養護老人ホーム名簿</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="78" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2施設・110人</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>3施設・160人</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2施設・42人</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>3施設・62人</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>5事業所・81人</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>7事業所・定員不明</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業所一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>注1）本表は北海道が公表する名簿によるものであり、受託者が事業所へ照会して得たものではない。名簿の時点は令和8年7月1日（サービス付き高齢者向け住宅のみ令和8年6月30日）であり、居所変更実態調査の令和7年4月1日とは時点が異なる。注2）住宅型有料老人ホーム及びサービス付き高齢者向け住宅は介護保険の指定サービスではないため、入居者は在宅サービス（訪問介護・通所介護等）を利用する。見込量の算定においては在宅に含まれており、居住系には含まれない。注3）サービス付き高齢者向け住宅の名簿は住所地特例が適用されるものの一覧であり、札幌市・旭川市・函館市分を含まない。住所地特例が適用されないサービス付き高齢者向け住宅が区域内にある可能性は残る（05シート）。</t>
         </is>
@@ -1021,8 +1224,553 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A19:E19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>特別養護老人ホームの定員</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム名簿（令和8年7月1日現在）により、区域内の特別養護老人ホーム及び地域密着型介護老人福祉施設の定員が確定した。居所変更実態調査では2施設が未回答であり、定員が把握できていなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>施設名</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>定員</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>うち地域密着型</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>ショート専用</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ショート空床</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>運営主体</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町特別養護老人ホームアゼリアハイツ</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>利用可</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>(社福)東神楽町社会福祉協議会</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町特別養護老人ホームアゼリアハイツ（ユニット型）</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>利用可</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>(社福)東神楽町社会福祉協議会</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム東川町羽衣園</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>利用可</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設 美瑛慈光園</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>利用可</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光会</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム美瑛慈光園</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光会</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園サテライト特養 燈</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>利用可</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光会</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>計　6施設</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>222</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>【調査及び見える化との突合】</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>名簿</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>調査</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>見える化
+事業所数</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設（広域型）</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>3施設・160人</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2施設・110人</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>+50人</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町特別養護老人ホームアゼリアハイツ（定員50人）が居所変更実態調査に回答していない。定員160人は、資料依頼No.6③の「介護老人福祉施設の定員減少234人→160人」の160人と一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>3施設・62人</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2施設・42人</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>+20人</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>アゼリアハイツ（ユニット型・定員20人）が回答していない。残る2施設は美瑛慈光会による地域密着型美瑛慈光園24人とサテライト特養燈18人である</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>【施設サービスの区域内定員（訂正）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>これまで</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>訂正後</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>110人（調査2施設）</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>160人（名簿3施設）</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>アゼリアハイツ50人を加えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>42人（調査2施設）</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>62人（名簿3施設）</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>アゼリアハイツ（ユニット型）20人を加えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>240人（調査3施設）</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>240人（変わらない）</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>見える化K1c（3事業所）と一致し、すべて把握している</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>施設サービス　計</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>392人</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>462人</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度の見込量339人に対し、なお余裕がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="65" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>注1）ショート専用定員21人のほか、4施設で空床利用が可能である。短期入所生活介護の見込量（将来推計 第2段階04シート）と対照する。注2）介護老人保健施設の定員は本名簿の対象外であり、居所変更実態調査の3施設240人による。見える化K1c（3事業所）と施設数が一致するため、区域内のすべてを把握している。注3）グループホームの定員は本名簿の対象外である。調査で5事業所81人を把握しているが、名簿では7事業所ある（07シート）。新たに2事業所の定員が不明であり、介護サービス情報公表システム又は広域連合の台帳による。注4）本シートにより資料依頼No.6②（施設・居住系の定員）のうち定員の部分は解消した。入所者数・空床・休止床は引き続き確認を要する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4107,4 +4855,1972 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>指定事業所一覧と見える化の事業所数の突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧（令和8年6月30日現在）から区域内の事業所を抽出し、見える化システムのK系列（令和6年度）と突合する。両者は1年8か月の時点差があるため、差はこの間の開設・廃止によるものと考えられる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>名簿
+R8.6.30</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>見える化
+R6年度</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>一致する。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり（点検事項No.23）、母数13が確定した</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>名簿が1少ない。医療機関のみなし指定は指定事業所一覧に載らないため、老健又は病院によるものが名簿から漏れている可能性がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>一致する。4事業所のうち3事業所が美瑛町にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>一致する。5事業所すべてが社会福祉法人美瑛慈光会により美瑛町で運営されている（08シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>名簿が2多い。グループホームファミリー（東川町・株式会社SORA）とグループホームくるみの郷（東川町・有限会社プランタン東川）が見える化の令和6年度の値には含まれていない。居所変更実態調査にも回答がなく、定員が把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>一致する。定員156人（03シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>一致する。定員160人（09シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>一致する。定員62人（09シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>一致する。定員240人（調査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>名簿が3多い。この間に開設した事業所があると考えられる。在宅生活改善調査の事業所票は居宅介護支援10事業所から受領しており、母数が10か13かで回収率の評価が変わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="D18" s="14" t="inlineStr"/>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>13区分のうち10区分が一致した</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>注1）名簿は令和8年6月30日現在、見える化K系列は令和6年度（令和6年10月1日現在）である。時点が1年8か月異なる。注2）13区分のうち10区分で事業所数が一致した。見える化の事業所数は保険者の区域内の事業所を数えたものであり、名簿から区域内を抽出した結果と一致することが確かめられた。これにより、見える化のK系列を区域内の事業所数として用いてよいことが裏付けられた。注3）区域内の指定事業所は延べ124件である（介護予防・総合事業の区分を含む）。同一の事業所が複数の区分に登録されているため、実事業所数はこれより少ない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A20:E20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>通常の事業の実施地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧に収録された「通常の事業実施地域」により、区域内の事業所がどの町を対象としているかを整理する。資料依頼No.10・確認No.15（訪問・通所困難地域の判定の根拠）に対応するものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>【訪問介護　13事業所】　在宅生活の継続に最も影響する</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>所在町</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>通常の事業実施地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>花時計訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡東神楽町 上川郡当麻町 上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所ひばり</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 ほがらか</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>東川町社協訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護ステーション ゆう</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡鷹栖町 上川郡当麻町 上川郡比布町 上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>ヘルパーステーション フラワー</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>（記載なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>（記載なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所 恩送り</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>（記載なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡美瑛町 空知郡上富良野町</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>対象としている事業所数</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr"/>
+      <c r="C34" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>「記載なし」は名簿の実施地域欄が空欄のものである。所在町を対象としているとみるのが自然だが、確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>【訪問看護　7事業所】　医療的ケアの受け皿</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>所在町</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>通常の事業実施地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問看護事業所ひばり</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>花時計訪問看護ステーション</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡東神楽町</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護ステーション ゆう</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護ステーション れもねーど</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 深川市 上川郡鷹栖町 上川郡東神楽町 上川郡当麻町 上川郡比布町 上川郡愛別町 上川郡上川町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護事業所恩送り</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>（記載なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>一般社団法人北海道総合在宅ケア事業団 美瑛訪問看護ステーション</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>対象としている事業所数</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr"/>
+      <c r="C45" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>「記載なし」は名簿の実施地域欄が空欄のものである。所在町を対象としているとみるのが自然だが、確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>【通所介護（一般）　2事業所】</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>所在町</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>通常の事業実施地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町デイサービスセンター</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡東神楽町 上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>デイサービス ゆう</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>対象としている事業所数</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr"/>
+      <c r="C51" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>「記載なし」は名簿の実施地域欄が空欄のものである。所在町を対象としているとみるのが自然だが、確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>【地域密着型通所介護　4事業所】　区域内の被保険者のみが利用できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>所在町</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>通常の事業実施地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>東川町デイサービスセンター</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園デイサービスセンター</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>デイサービスセンターあすか</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>慈光園あるくらぶ輪</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>対象としている事業所数</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr"/>
+      <c r="C59" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>「記載なし」は名簿の実施地域欄が空欄のものである。所在町を対象としているとみるのが自然だが、確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>【小規模多機能型居宅介護　5事業所】　在宅生活改善調査の回答の偏りに関係する</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>所在町</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>通常の事業実施地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園小規模多機能「虹」</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園小規模多機能「七彩」</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園小規模多機能「燈」</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園小規模多機能 ひなた</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町 空知郡上富良野町 空知郡中富良野町</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園小規模多機能ほたる</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>対象としている事業所数</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr"/>
+      <c r="C68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>「記載なし」は名簿の実施地域欄が空欄のものである。所在町を対象としているとみるのが自然だが、確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>【居宅介護支援　13事業所】　計画作成の担い手</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>所在町</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>通常の事業実施地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>回生苑 居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡鷹栖町 上川郡東神楽町 上川郡当麻町 上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町ケアプラン相談センター</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>指定居宅介護支援事業所ひばり</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>東川町社協居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>ひだまりの里居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援事業所 ゆう</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>ひがしかわ介護相談センター</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡東神楽町 上川郡東川町</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援事業所 おうか</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 上川郡東神楽町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>ほの香 居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ケアプラン相談センター</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 富良野市 上川郡当麻町 上川郡東川町 上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>上川郡美瑛町</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>ライフデザイン陽風</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>旭川市 富良野市 上川郡東神楽町 上川郡東川町 上川郡美瑛町 空知郡上富良野町</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>対象としている事業所数</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr"/>
+      <c r="C85" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D85" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E85" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>「記載なし」は名簿の実施地域欄が空欄のものである。所在町を対象としているとみるのが自然だが、確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="104" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>注1）「通常の事業の実施地域」は運営規程に定めるものであり、これを超えて利用する場合は交通費等の実費を負担することがある。実施地域外であっても利用できないわけではない。注2）小規模多機能型居宅介護は5事業所すべてが社会福祉法人美瑛慈光会により美瑛町で運営されており、東川町・東神楽町を実施地域とするのは「七彩」1事業所のみである。在宅生活改善調査の利用者票99票のうち36票が同一法人の小規模多機能2事業所からの提出であり（点検事項No.2）、区域内の小規模多機能がすべて1法人であるという構造がその背景にある。注3）地域密着型通所介護4事業所のうち3事業所が美瑛町にあり、うち2事業所は美瑛町のみを実施地域としている。注4）訪問介護13事業所のうち3事業所は実施地域欄が空欄である。空欄の3事業所（フラワー・桜華・恩送り）はいずれも東川町に所在し、いずれも令和以降に指定を受けた比較的新しい事業所である。注5）本シートは第1章第7節（訪問・通所困難地域）の根拠となる。確認No.15（運営規程の実施地域）は本名簿により解消した。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A87:F87"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_指定事業所一覧と見える化の事業所数の突合" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_通常の事業の実施地域" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_特別養護老人ホームの定員" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公表システムの個別画面による確認" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -226,10 +227,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -620,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -687,7 +688,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>将来推計 第2段階06シートの「居住系の見込量145人が区域内定員139人を上回る」という記述は、定員の把握漏れによるものであった。居住系の区域内定員はグループホーム81人＋特定施設156人＝237人であり、見込量145人は定員内に収まる。同シートを訂正する。</t>
+          <t>将来推計 第2段階06シートの「居住系の見込量145人が区域内定員139人を上回る」という記述は、定員の把握漏れによるものであった。居住系の区域内定員はグループホーム99人＋特定施設156人＝255人であり、見込量145人は定員内に収まる。同シートを訂正する。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -996,226 +997,276 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>グループホームファミリーの定員は18人である</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システムの個別画面（記入日 令和7年10月20日）により、グループホームファミリー（東川町北町5丁目）は2ユニット18人、入居率100％、総従業者数15人（介護職員は常勤12人）であることが確認された。運営は株式会社SORAで、介護付きホームファミリー（特定施設36人）と同一法人である。</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>居住系の区域内定員は、グループホーム99人（調査5事業所81人＋ファミリー18人）＋特定施設156人＝255人となる。令和11年度の見込量145人は56.9％であり、定員に余裕がある。従業者数は個別画面にしかない項目であり、職員数の突合はこの方法によることが実証された。</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="100" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>グループホームくるみの郷は公表システムに掲載がない</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧には掲載されている（有限会社プランタン東川・東川町北町3丁目2番7号・事業所番号0173100371）が、公表システムの位置情報付きデータにも個別画面にも見当たらない。同一の所在地に住宅型有料老人ホームわくらばⅡ（定員18人・住所地特例適用開始 令和5年6月1日）が届出されている。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。定員・休止の状況は発注者自身が保有しているため、資料依頼No.5（指定事業所台帳）に含めてご提供いただく。区域内で定員が未確定なのは本事業所のみとなった。</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>【供給量の新旧】</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>これまで（調査による）</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>今回（公表名簿による）</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>差</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>出典</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>特定施設（介護付有料）</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2施設・58人</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>3施設・156人</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>特定施設一覧・K2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ホーム</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>3施設・91人</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>9施設・223人</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>届出済有料老人ホーム一覧</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>サービス付き高齢者向け住宅</t>
+          <t>特定施設（介護付有料）</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>1件・30戸</t>
+          <t>2施設・58人</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2件・66戸</t>
+          <t>3施設・156人</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>住所地特例適用施設一覧</t>
+          <t>特定施設一覧・K2a</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>軽費老人ホーム（ケアハウス）</t>
+          <t>住宅型有料老人ホーム</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>3施設・91人</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1施設・50人</t>
+          <t>9施設・223人</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>軽費老人ホーム名簿</t>
+          <t>届出済有料老人ホーム一覧</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>養護老人ホーム</t>
+          <t>サービス付き高齢者向け住宅</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>1件・30戸</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>区域内になし</t>
+          <t>2件・66戸</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>養護老人ホーム名簿</t>
+          <t>住所地特例適用施設一覧</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>介護老人福祉施設</t>
+          <t>軽費老人ホーム（ケアハウス）</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2施設・110人</t>
+          <t>―</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>3施設・160人</t>
+          <t>1施設・50人</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>特別養護老人ホーム名簿</t>
+          <t>軽費老人ホーム名簿</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>地域密着型介護老人福祉施設</t>
+          <t>養護老人ホーム</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2施設・42人</t>
+          <t>―</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>3施設・62人</t>
+          <t>区域内になし</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>特別養護老人ホーム名簿</t>
+          <t>養護老人ホーム名簿</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護</t>
+          <t>介護老人福祉施設</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>5事業所・81人</t>
+          <t>2施設・110人</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>7事業所・定員不明</t>
+          <t>3施設・160人</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>介護保険事業所一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="78" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+          <t>特別養護老人ホーム名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2施設・42人</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>3施設・62人</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>5事業所・81人</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>7事業所・99人＋くるみの郷</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業所一覧・公表システム</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="78" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>注1）本表は北海道が公表する名簿によるものであり、受託者が事業所へ照会して得たものではない。名簿の時点は令和8年7月1日（サービス付き高齢者向け住宅のみ令和8年6月30日）であり、居所変更実態調査の令和7年4月1日とは時点が異なる。注2）住宅型有料老人ホーム及びサービス付き高齢者向け住宅は介護保険の指定サービスではないため、入居者は在宅サービス（訪問介護・通所介護等）を利用する。見込量の算定においては在宅に含まれており、居住系には含まれない。注3）サービス付き高齢者向け住宅の名簿は住所地特例が適用されるものの一覧であり、札幌市・旭川市・函館市分を含まない。住所地特例が適用されないサービス付き高齢者向け住宅が区域内にある可能性は残る（05シート）。</t>
         </is>
@@ -1224,8 +1275,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1771,6 +1822,510 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システムの個別画面による確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>公表システムのオープンデータには従業者数が含まれないため、個別事業所の公表画面が従業者数の唯一の出所である。令和8年8月5日にグループホームファミリーの公表画面を受領し、定員と従業者数を確認した。同じくグループホームくるみの郷を探したが、公表システムに掲載が見つからなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>【グループホームファミリー（東川町）】公表画面　記入日 2025-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>上川郡東川町北町5丁目4-10</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>介護付きホームファミリー（特定施設・定員36人）と同じ北町5丁目にあり、いずれも株式会社SORAが運営する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>事業開始年月日</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2006-02-01</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>平成18年2月開設。見える化K2cが令和6年度に5事業所となっている理由は本事業所の新設によるものではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>利用定員</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2ユニット18人（都道府県平均15.2人）</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>居所変更実態調査で把握していなかったグループホームの定員が確定した。区域内のグループホームの定員は調査の81人に18人を加えて99人となる</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>入居率</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>満室である。居住系の定員に余裕があるとしても、個々の事業所には空きがない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>入居者の平均年齢</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>90歳</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>男性2人・女性15人。要介護4が6人と最も多い</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>総従業者数</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>15人</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>計画作成担当者2人（常勤）・介護職員12人（常勤）・看護師0人。介護人材実態調査には本事業所からの回答がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>介護職員数</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>常勤12人・非常勤0人</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査で把握したグループホームの介護職員数に本事業所の12人は含まれていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>介護職員の退職者数</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>常勤2人</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>オープンデータにはない項目である。介護人材実態調査の離職65人との対照に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>経験年数5年以上の介護職員の割合</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>41.7％</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査の勤続年数の分布（勤続1年未満19.9％）と対照できる項目である</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>夜勤を行う従業者数</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2ユニットで夜勤2人。人員配置基準を満たしている</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>法人等が実施するサービス</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護／認知症対応型共同生活介護／介護予防特定施設入居者生活介護／介護予防認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>株式会社SORAは特定施設（介護付きホームファミリー36人）とグループホーム（18人）の両方を運営している。居住系の区域内定員のうち54人が同一法人による</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>【グループホームくるみの郷（東川町）】公表システムに掲載が見つからない</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>確認したもの</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧（R8.6.30）</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>掲載あり</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>有限会社プランタン東川、事業所番号0173100371、東川町北町3丁目2番7号。指定は現に有効である</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>公表システムの位置情報付きデータ</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>掲載なし</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>区域内の認知症対応型共同生活介護6事業所のうちに含まれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>公表システムの個別画面</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>見つからない</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>発注者において検索したが掲載が確認できなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>見える化K2c（令和6年度）</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>5事業所</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>調査で把握した5事業所と一致するため、本事業所は含まれていないとみられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>同一所在地の届出</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームわくらばⅡ</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>株式会社北海道光健康社・定員18人・住所地特例適用開始 令和5年6月1日。グループホームくるみの郷と同じ住所である</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>【くるみの郷の取扱い　受託者の案】</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>考えられること</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>確かめ方</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>休止している。介護サービス情報の公表制度は前年度の介護報酬収入が一定額以下の事業所を報告の対象外としており、休止中の事業所は公表画面が作られない。指定は有効なまま北海道の一覧に残る。</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>広域連合が指定権者であるため、休止届の有無を確認できる</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>同一の建物で住宅型有料老人ホームわくらばⅡに転換した。わくらばⅡの住所地特例適用開始が令和5年6月であり、見える化K2cが令和4年度に6事業所から5事業所へ減っている時期と近い。ただし設置法人が異なる。</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>同上。指定の休止・廃止の届出と、わくらばⅡの届出の関係を確認できる</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>稼働しているが公表の報告を行っていない。この場合は公表制度上の未報告であり、北海道の所管となる。</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>広域連合から北海道へ照会する</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n"/>
+    </row>
+    <row r="32" ht="104" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.5（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2965,7 +3520,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>認知症対応型共同生活介護</t>
@@ -2980,14 +3535,12 @@
       <c r="D6" s="13" t="n">
         <v>81</v>
       </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E6" s="13" t="n">
+        <v>99</v>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>事業所数が一致する。名簿はグループホームを収録しないため定員の突合はできないが、調査で5事業所81人を把握済み</t>
+          <t>見える化は令和6年度5事業所だが、北海道の介護保険事業所一覧（令和8年6月30日現在）は7事業所である。公表システムの個別画面でファミリー18人を確認し99人とした。くるみの郷は掲載がなく未確定である（10シート）</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3566,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>区域内に事業所がない。軽費老人ホーム名簿の地特定指定欄も空欄であり整合する</t>
         </is>
@@ -3039,7 +3592,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>調査は2施設のみで1施設が未回答（点検事項No.9〜No.12）。名簿は特別養護老人ホームを収録しないため、定員は発注者への照会又は介護サービス情報公表システムによる</t>
         </is>
@@ -3065,7 +3618,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>調査は2施設のみで1施設が未回答。上に同じ</t>
         </is>
@@ -3091,7 +3644,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>事業所数が一致する。3施設240人を把握済み</t>
         </is>
@@ -3169,14 +3722,14 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>81人</t>
+          <t>99人</t>
         </is>
       </c>
       <c r="D15" s="22" t="n"/>
       <c r="E15" s="23" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>調査で5事業所すべてを把握しており変わらない</t>
+          <t>北海道の介護保険事業所一覧では7事業所ある。公表システムの個別画面によりファミリー18人を確認して加えた。くるみの郷は掲載がなく未確定である（10シート）</t>
         </is>
       </c>
     </row>
@@ -3215,16 +3768,16 @@
           <t>139人</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>237人</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>255人</t>
         </is>
       </c>
       <c r="D17" s="22" t="n"/>
       <c r="E17" s="23" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上記の合計</t>
+          <t>上記の合計。グループホームは調査の5事業所81人に、公表システムで確認したファミリー18人を加えた99人による（10シート）</t>
         </is>
       </c>
     </row>
@@ -3263,9 +3816,9 @@
           <t>104.3％（定員超過）</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>61.2％（定員内）</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>56.9％（定員内）</t>
         </is>
       </c>
       <c r="D19" s="22" t="n"/>
@@ -3279,7 +3832,7 @@
     <row r="21" ht="78" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>注1）見える化K系列の事業所数は令和6年度の値である。名簿は令和8年7月1日現在であり時点が異なるが、K2aは平成24年度から令和6年度まで一貫して3事業所であり、この間の増減はない。注2）居住系の見込量145人は大雪地区広域連合の被保険者のうち居住系サービスを受給する者の数である。区域内の施設には住所地特例により他の保険者の被保険者も入居しており、定員237人と見込量145人の差がそのまま空きを示すものではない。居所変更実態調査では特定施設の新規入所の84.2％が区域外からの入所であった。注3）特別養護老人ホーム・地域密着型特別養護老人ホーム・介護老人保健施設・グループホームは、今回受領した名簿の対象外である。定員は介護サービス情報公表システム又は発注者への照会による。</t>
+          <t>注1）見える化K系列の事業所数は令和6年度の値である。名簿は令和8年7月1日現在であり時点が異なるが、K2aは平成24年度から令和6年度まで一貫して3事業所であり、この間の増減はない。注2）居住系の見込量145人は大雪地区広域連合の被保険者のうち居住系サービスを受給する者の数である。区域内の施設には住所地特例により他の保険者の被保険者も入居しており、定員255人と見込量145人の差がそのまま空きを示すものではない。居所変更実態調査では特定施設の新規入所の84.2％が区域外からの入所であった。注3）特別養護老人ホーム・地域密着型特別養護老人ホーム・介護老人保健施設・グループホームは、今回受領した名簿の対象外である。定員は介護サービス情報公表システム又は発注者への照会による。</t>
         </is>
       </c>
     </row>
@@ -4580,7 +5133,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>将来推計 第2段階06シートの居住系の定員を237人に改め、「見込量が区域内定員を上回る」という記述を削除する。定員内に収まる旨に改める。</t>
+          <t>将来推計 第2段階06シートの居住系の定員を255人に改め、「見込量が区域内定員を上回る」という記述を削除する。定員内に収まる旨に改める。</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1047,136 +1047,138 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="20" ht="100" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>さわやか東神楽館の入居者は軽度者が7割である</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>公表画面（記入日 令和7年10月6日）により、定員100人・入居者97人・入居率100％、要支援1・2が26人（26.8％）、要介護1が42人（43.3％）で、要支援1〜要介護1が68人（70.1％）を占めることが確認された。介護職員31人（常勤15・非常勤16）、介護職員の退職者数11人、昨年度の退居者22人である。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>居所変更実態調査に回答していない区域内最大の特定施設について、定員・入居者数・要介護度別の内訳・従業者数を補うことができた。特定施設は定員156人に対し入居者154人（98.7％）でほぼ満室である。入所前の居場所と退去先は公表されていないため補えない。</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>【供給量の新旧】</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>これまで（調査による）</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>今回（公表名簿による）</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>差</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>出典</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>特定施設（介護付有料）</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2施設・58人</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>3施設・156人</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>特定施設一覧・K2a</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ホーム</t>
+          <t>特定施設（介護付有料）</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3施設・91人</t>
+          <t>2施設・58人</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>9施設・223人</t>
+          <t>3施設・156人</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>届出済有料老人ホーム一覧</t>
+          <t>特定施設一覧・K2a</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>サービス付き高齢者向け住宅</t>
+          <t>住宅型有料老人ホーム</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>1件・30戸</t>
+          <t>3施設・91人</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2件・66戸</t>
+          <t>9施設・223人</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>住所地特例適用施設一覧</t>
+          <t>届出済有料老人ホーム一覧</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>軽費老人ホーム（ケアハウス）</t>
+          <t>サービス付き高齢者向け住宅</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>1件・30戸</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>1施設・50人</t>
+          <t>2件・66戸</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>軽費老人ホーム名簿</t>
+          <t>住所地特例適用施設一覧</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>養護老人ホーム</t>
+          <t>軽費老人ホーム（ケアハウス）</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1186,53 +1188,53 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>区域内になし</t>
+          <t>1施設・50人</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>養護老人ホーム名簿</t>
+          <t>軽費老人ホーム名簿</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>介護老人福祉施設</t>
+          <t>養護老人ホーム</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2施設・110人</t>
+          <t>―</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>3施設・160人</t>
+          <t>区域内になし</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>特別養護老人ホーム名簿</t>
+          <t>養護老人ホーム名簿</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>地域密着型介護老人福祉施設</t>
+          <t>介護老人福祉施設</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2施設・42人</t>
+          <t>2施設・110人</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3施設・62人</t>
+          <t>3施設・160人</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
@@ -1245,28 +1247,51 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護</t>
+          <t>地域密着型介護老人福祉施設</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>5事業所・81人</t>
+          <t>2施設・42人</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>7事業所・99人＋くるみの郷</t>
+          <t>3施設・62人</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>特別養護老人ホーム名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>5事業所・81人</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>7事業所・99人＋くるみの郷</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>介護保険事業所一覧・公表システム</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="78" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="78" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>注1）本表は北海道が公表する名簿によるものであり、受託者が事業所へ照会して得たものではない。名簿の時点は令和8年7月1日（サービス付き高齢者向け住宅のみ令和8年6月30日）であり、居所変更実態調査の令和7年4月1日とは時点が異なる。注2）住宅型有料老人ホーム及びサービス付き高齢者向け住宅は介護保険の指定サービスではないため、入居者は在宅サービス（訪問介護・通所介護等）を利用する。見込量の算定においては在宅に含まれており、居住系には含まれない。注3）サービス付き高齢者向け住宅の名簿は住所地特例が適用されるものの一覧であり、札幌市・旭川市・函館市分を含まない。住所地特例が適用されないサービス付き高齢者向け住宅が区域内にある可能性は残る（05シート）。</t>
         </is>
@@ -1275,8 +1300,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1833,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1860,7 +1885,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>【グループホームファミリー（東川町）】公表画面　記入日 2025-10-20</t>
+          <t>【さわやか東神楽館（東神楽町・特定施設）】公表画面　記入日 2025-10-06</t>
         </is>
       </c>
     </row>
@@ -1886,446 +1911,753 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>所在地</t>
+          <t>入居定員</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>上川郡東川町北町5丁目4-10</t>
+          <t>100人（都道府県平均63.2人）</t>
         </is>
       </c>
       <c r="C6" s="22" t="n"/>
       <c r="D6" s="23" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>介護付きホームファミリー（特定施設・定員36人）と同じ北町5丁目にあり、いずれも株式会社SORAが運営する</t>
+          <t>区域内最大の特定施設。道平均の1.6倍の規模である</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>事業開始年月日</t>
+          <t>入居率</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>100％</t>
         </is>
       </c>
       <c r="C7" s="22" t="n"/>
       <c r="D7" s="23" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>平成18年2月開設。見える化K2cが令和6年度に5事業所となっている理由は本事業所の新設によるものではない</t>
+          <t>満室である。居住系の区域内定員に余裕があっても、個々の施設には空きがない</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>利用定員</t>
+          <t>入居者数</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2ユニット18人（都道府県平均15.2人）</t>
+          <t>97人（男25人・女72人）</t>
         </is>
       </c>
       <c r="C8" s="22" t="n"/>
       <c r="D8" s="23" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>居所変更実態調査で把握していなかったグループホームの定員が確定した。区域内のグループホームの定員は調査の81人に18人を加えて99人となる</t>
+          <t>居所変更実態調査に回答していないため、同調査の特定施設の集計（入所者57人）には含まれていない</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>入居率</t>
+          <t>入居者の平均年齢</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>100％</t>
+          <t>88.7歳</t>
         </is>
       </c>
       <c r="C9" s="22" t="n"/>
       <c r="D9" s="23" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>満室である。居住系の定員に余裕があるとしても、個々の事業所には空きがない</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>入居者の平均年齢</t>
+          <t>要支援1・2</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>90歳</t>
+          <t>26人（26.8％）</t>
         </is>
       </c>
       <c r="C10" s="22" t="n"/>
       <c r="D10" s="23" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>男性2人・女性15人。要介護4が6人と最も多い</t>
+          <t>特定施設に要支援者が26人入居している。居住系サービスの見込量を要介護度別に置く際、要支援の利用率を無視できない</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>総従業者数</t>
+          <t>要介護1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>15人</t>
+          <t>42人（43.3％）</t>
         </is>
       </c>
       <c r="C11" s="22" t="n"/>
       <c r="D11" s="23" t="n"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>計画作成担当者2人（常勤）・介護職員12人（常勤）・看護師0人。介護人材実態調査には本事業所からの回答がない</t>
+          <t>単独で最多。認定者全体で要介護1への集中がみられることと同じ方向である</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>介護職員数</t>
+          <t>要支援1〜要介護1</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>常勤12人・非常勤0人</t>
+          <t>68人（70.1％）</t>
         </is>
       </c>
       <c r="C12" s="22" t="n"/>
       <c r="D12" s="23" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査で把握したグループホームの介護職員数に本事業所の12人は含まれていない</t>
+          <t>軽度者が7割を占める。特定施設が重度者の受け皿として機能しているとは限らない。第6章第4節（整備の方針）の判断材料となる</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>介護職員の退職者数</t>
+          <t>要介護4・5</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>常勤2人</t>
+          <t>9人（9.3％）</t>
         </is>
       </c>
       <c r="C13" s="22" t="n"/>
       <c r="D13" s="23" t="n"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>オープンデータにはない項目である。介護人材実態調査の離職65人との対照に用いる</t>
+          <t>重度者は9人にとどまる</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>経験年数5年以上の介護職員の割合</t>
+          <t>昨年度の退居者数</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>41.7％</t>
+          <t>22人</t>
         </is>
       </c>
       <c r="C14" s="22" t="n"/>
       <c r="D14" s="23" t="n"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査の勤続年数の分布（勤続1年未満19.9％）と対照できる項目である</t>
+          <t>入居者97人に対し22.7％。居所変更実態調査では把握できていない</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>夜勤を行う従業者数</t>
+          <t>総従業者数</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2人</t>
+          <t>43人</t>
         </is>
       </c>
       <c r="C15" s="22" t="n"/>
       <c r="D15" s="23" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2ユニットで夜勤2人。人員配置基準を満たしている</t>
+          <t>看護職員7人（常勤5・非常勤2）、介護職員31人（常勤15・非常勤16）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>法人等が実施するサービス</t>
+          <t>介護職員数</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護／認知症対応型共同生活介護／介護予防特定施設入居者生活介護／介護予防認知症対応型共同生活介護</t>
+          <t>31人（常勤15人・非常勤16人）</t>
         </is>
       </c>
       <c r="C16" s="22" t="n"/>
       <c r="D16" s="23" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>株式会社SORAは特定施設（介護付きホームファミリー36人）とグループホーム（18人）の両方を運営している。居住系の区域内定員のうち54人が同一法人による</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>【グループホームくるみの郷（東川町）】公表システムに掲載が見つからない</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>確認したもの</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr">
+          <t>介護人材実態調査に含まれていない31人である。非常勤が半数を占め、区域内の他施設と比べ非常勤の割合が高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>介護職員の退職者数</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>11人（常勤5人・非常勤6人）</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>介護職員31人に対し35.5％。介護人材実態調査の離職65人には含まれていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>経験年数10年以上の介護職員の割合</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>16.1％</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>グループホームファミリーは経験5年以上が41.7％であり、設問の年数が異なるため直接比較できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>第三者評価</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>記入日前4年間に実施していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>【グループホームファミリー（東川町）】公表画面　記入日 2025-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>北海道の介護保険事業所一覧（R8.6.30）</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>掲載あり</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>有限会社プランタン東川、事業所番号0173100371、東川町北町3丁目2番7号。指定は現に有効である</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>公表システムの位置情報付きデータ</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>掲載なし</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>区域内の認知症対応型共同生活介護6事業所のうちに含まれない</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>公表システムの個別画面</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>見つからない</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>発注者において検索したが掲載が確認できなかった</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>見える化K2c（令和6年度）</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>5事業所</t>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>上川郡東川町北町5丁目4-10</t>
         </is>
       </c>
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>調査で把握した5事業所と一致するため、本事業所は含まれていないとみられる</t>
+          <t>介護付きホームファミリー（特定施設・定員36人）と同じ北町5丁目にあり、いずれも株式会社SORAが運営する</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>同一所在地の届出</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ホームわくらばⅡ</t>
+          <t>事業開始年月日</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>平成18年2月開設。見える化K2cが令和6年度に5事業所となっている理由は本事業所の新設によるものではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>利用定員</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2ユニット18人（都道府県平均15.2人）</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>居所変更実態調査で把握していなかったグループホームの定員が確定した。区域内のグループホームの定員は調査の81人に18人を加えて99人となる</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>入居率</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>満室である。居住系の定員に余裕があるとしても、個々の事業所には空きがない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>入居者の平均年齢</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>90歳</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>男性2人・女性15人。要介護4が6人と最も多い</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>総従業者数</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>15人</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>計画作成担当者2人（常勤）・介護職員12人（常勤）・看護師0人。介護人材実態調査には本事業所からの回答がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>介護職員数</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>常勤12人・非常勤0人</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査で把握したグループホームの介護職員数に本事業所の12人は含まれていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>介護職員の退職者数</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>常勤2人</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>オープンデータにはない項目である。介護人材実態調査の離職65人との対照に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>経験年数5年以上の介護職員の割合</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>41.7％</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査の勤続年数の分布（勤続1年未満19.9％）と対照できる項目である</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>夜勤を行う従業者数</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>2ユニットで夜勤2人。人員配置基準を満たしている</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>法人等が実施するサービス</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護／認知症対応型共同生活介護／介護予防特定施設入居者生活介護／介護予防認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>株式会社SORAは特定施設（介護付きホームファミリー36人）とグループホーム（18人）の両方を運営している。居住系の区域内定員のうち54人が同一法人による</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>【グループホームくるみの郷（東川町）】公表システムに掲載が見つからない</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>確認したもの</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧（R8.6.30）</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>掲載あり</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>有限会社プランタン東川、事業所番号0173100371、東川町北町3丁目2番7号。指定は現に有効である</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>公表システムの位置情報付きデータ</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>掲載なし</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>区域内の認知症対応型共同生活介護6事業所のうちに含まれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>公表システムの個別画面</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>見つからない</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>発注者において検索したが掲載が確認できなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>見える化K2c（令和6年度）</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>5事業所</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>調査で把握した5事業所と一致するため、本事業所は含まれていないとみられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>同一所在地の届出</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームわくらばⅡ</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>株式会社北海道光健康社・定員18人・住所地特例適用開始 令和5年6月1日。グループホームくるみの郷と同じ住所である</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>【くるみの郷の取扱い　受託者の案】</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>考えられること</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>確かめ方</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>休止している。介護サービス情報の公表制度は前年度の介護報酬収入が一定額以下の事業所を報告の対象外としており、休止中の事業所は公表画面が作られない。指定は有効なまま北海道の一覧に残る。</t>
         </is>
       </c>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>広域連合が指定権者であるため、休止届の有無を確認できる</t>
         </is>
       </c>
-      <c r="E28" s="23" t="n"/>
-    </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="E45" s="23" t="n"/>
+    </row>
+    <row r="46" ht="48" customHeight="1">
+      <c r="A46" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>同一の建物で住宅型有料老人ホームわくらばⅡに転換した。わくらばⅡの住所地特例適用開始が令和5年6月であり、見える化K2cが令和4年度に6事業所から5事業所へ減っている時期と近い。ただし設置法人が異なる。</t>
         </is>
       </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>同上。指定の休止・廃止の届出と、わくらばⅡの届出の関係を確認できる</t>
         </is>
       </c>
-      <c r="E29" s="23" t="n"/>
-    </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="E46" s="23" t="n"/>
+    </row>
+    <row r="47" ht="48" customHeight="1">
+      <c r="A47" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>稼働しているが公表の報告を行っていない。この場合は公表制度上の未報告であり、北海道の所管となる。</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>広域連合から北海道へ照会する</t>
         </is>
       </c>
-      <c r="E30" s="23" t="n"/>
-    </row>
-    <row r="32" ht="104" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="E47" s="23" t="n"/>
+    </row>
+    <row r="49" ht="104" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.5（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="42">
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="D47:E47"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -1858,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2412,19 +2412,19 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>【グループホームくるみの郷（東川町）】公表システムに掲載が見つからない</t>
+          <t>【グループホームびえいの郷（美瑛町）】公表画面　記入日 2025-10-04</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>確認したもの</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>結果</t>
+          <t>値</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
@@ -2435,229 +2435,396 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>北海道の介護保険事業所一覧（R8.6.30）</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>掲載あり</t>
+          <t>利用定員</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2ユニット18人</t>
         </is>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>有限会社プランタン東川、事業所番号0173100371、東川町北町3丁目2番7号。指定は現に有効である</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+          <t>居所変更実態調査の18人と一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>公表システムの位置情報付きデータ</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>掲載なし</t>
+          <t>入居率</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>95.9％</t>
         </is>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>区域内の認知症対応型共同生活介護6事業所のうちに含まれない</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>公表システムの個別画面</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>見つからない</t>
+          <t>介護職員数</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>常勤10人・非常勤7人（計17人）</t>
         </is>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>発注者において検索したが掲載が確認できなかった</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
+          <t>介護人材実態調査は介護職員16人・常勤10人と記入し、非常勤の欄が未記入である。常勤10人は一致し、未記入の非常勤は6人程度とみられる。点検事項の「合計と内訳の不一致」1件が説明できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>見える化K2c（令和6年度）</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>5事業所</t>
+          <t>介護職員の退職者数</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>常勤0人・非常勤1人</t>
         </is>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>調査で把握した5事業所と一致するため、本事業所は含まれていないとみられる</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>同一所在地の届出</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ホームわくらばⅡ</t>
+          <t>経験年数5年以上の介護職員の割合</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>94.1％</t>
         </is>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>グループホームファミリーの41.7％と対照的に高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>法人等が実施するサービス</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>訪問介護（びえいの郷・大町2丁目5番28号）／認知症対応型共同生活介護（びえいの郷・大町2丁目5番14号）</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス株式会社は、訪問介護（大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営している。住宅型有料老人ホームびえいの郷も大町2丁目5番28号にあり、訪問介護と併設である。介護人材実態調査で「有料1人・訪問介護13人」と分けて記入されていることと整合し、点検事項No.1（華の重複）の受託者の案を裏付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>留意</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>入居率95.9％（定員18人）に対し、要介護度別入所者数の合計及び男女別人数の合計はいずれも9人であり、公表画面の内部で整合しない。要介護度別の内訳は用いない。</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別の内訳は公表画面の内部で整合しないため用いない</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>【グループホームくるみの郷（東川町）】公表システムに掲載が見つからない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>確認したもの</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>北海道の介護保険事業所一覧（R8.6.30）</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>掲載あり</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>有限会社プランタン東川、事業所番号0173100371、東川町北町3丁目2番7号。指定は現に有効である</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>公表システムの位置情報付きデータ</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>掲載なし</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="23" t="n"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>区域内の認知症対応型共同生活介護6事業所のうちに含まれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>公表システムの個別画面</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>見つからない</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>発注者において検索したが掲載が確認できなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>見える化K2c（令和6年度）</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>5事業所</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>調査で把握した5事業所と一致するため、本事業所は含まれていないとみられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>同一所在地の届出</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームわくらばⅡ</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>株式会社北海道光健康社・定員18人・住所地特例適用開始 令和5年6月1日。グループホームくるみの郷と同じ住所である</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>【くるみの郷の取扱い　受託者の案】</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>考えられること</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>確かめ方</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="4" t="n">
+      <c r="E54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>休止している。介護サービス情報の公表制度は前年度の介護報酬収入が一定額以下の事業所を報告の対象外としており、休止中の事業所は公表画面が作られない。指定は有効なまま北海道の一覧に残る。</t>
         </is>
       </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>広域連合が指定権者であるため、休止届の有無を確認できる</t>
         </is>
       </c>
-      <c r="E45" s="23" t="n"/>
-    </row>
-    <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="4" t="n">
+      <c r="E55" s="23" t="n"/>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>同一の建物で住宅型有料老人ホームわくらばⅡに転換した。わくらばⅡの住所地特例適用開始が令和5年6月であり、見える化K2cが令和4年度に6事業所から5事業所へ減っている時期と近い。ただし設置法人が異なる。</t>
         </is>
       </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>同上。指定の休止・廃止の届出と、わくらばⅡの届出の関係を確認できる</t>
         </is>
       </c>
-      <c r="E46" s="23" t="n"/>
-    </row>
-    <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="4" t="n">
+      <c r="E56" s="23" t="n"/>
+    </row>
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>稼働しているが公表の報告を行っていない。この場合は公表制度上の未報告であり、北海道の所管となる。</t>
         </is>
       </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>広域連合から北海道へ照会する</t>
         </is>
       </c>
-      <c r="E47" s="23" t="n"/>
-    </row>
-    <row r="49" ht="104" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.5（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
+      <c r="E57" s="23" t="n"/>
+    </row>
+    <row r="59" ht="130" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.5（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）公表画面は3事業所分を受領した（グループホームファミリー・さわやか東神楽館・グループホームびえいの郷）。いずれも従業者数を事業所単位で確認できており、職員数の突合はこの方法によることが実証された。注5）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="50">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B38:D38"/>
-    <mergeCell ref="D45:E45"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B37:D37"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B51:D51"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="D47:E47"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B50:D50"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="D56:E56"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B43:D43"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -5473,10 +5473,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
+    <row r="23" ht="78" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>注1）未回答の9施設のうち8施設が介護保険の指定を受けない住まいである。居所変更実態調査は施設・居住系の事業所を対象としており、介護保険外の住まいへの配布が十分でなかった可能性がある。配布先の一覧は発注者にご確認いただきたい（点検事項No.29と同じ）。注2）さわやか東神楽館は特定施設入居者生活介護の指定を受けており、居所変更実態調査の対象に含まれるはずである。配布したが回収できなかったのか、配布先から漏れていたのかをご確認いただきたい。注3）住所地特例が適用されないサービス付き高齢者向け住宅は今回の名簿に載らない。北海道のサービス付き高齢者向け住宅の登録簿（サービス付き高齢者向け住宅情報提供システム）により網羅性を確認する必要がある。</t>
+          <t>注1）未回答は13施設（把握率58.1％）で、うち8施設が介護保険の指定を受けない住まいである。居所変更実態調査は施設・居住系の事業所を対象としており、介護保険外の住まいへの配布が十分でなかった可能性がある。配布先の一覧は発注者にご確認いただきたい（点検事項No.29と同じ）。注2）さわやか東神楽館は特定施設入居者生活介護の指定を受けており、居所変更実態調査の対象に含まれるはずである。配布したが回収できなかったのか、配布先から漏れていたのかをご確認いただきたい。注3）住所地特例が適用されないサービス付き高齢者向け住宅は今回の名簿に載らない。北海道のサービス付き高齢者向け住宅の登録簿（サービス付き高齢者向け住宅情報提供システム）により網羅性を確認する必要がある。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>さわやか東神楽館の入居者は軽度者が7割である</t>
+          <t>【参考】さわやか東神楽館の入居者の要介護度構成</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2037,7 +2037,7 @@
       <c r="D12" s="23" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>軽度者が7割を占める。特定施設が重度者の受け皿として機能しているとは限らない。第6章第4節（整備の方針）の判断材料となる</t>
+          <t>【参考】本施設では軽度者が7割を占める。特定施設が重度者の受け皿として機能しているとは限らない。1施設・1時点の値であり、同一時点の区域内3施設のデータへ更新するまで整備の必要量の算定には使用しない</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。定員・休止の状況は発注者自身が保有しているため、資料依頼No.5（指定事業所台帳）に含めてご提供いただく。区域内で定員が未確定なのは本事業所のみとなった。</t>
+          <t>認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。定員・休止の状況は発注者自身が保有しているため、資料依頼No.18（指定事業所台帳）に含めてご提供いただく。区域内で定員が未確定なのは本事業所のみとなった。</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -2769,7 +2769,7 @@
     <row r="59" ht="130" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.5（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）公表画面は3事業所分を受領した（グループホームファミリー・さわやか東神楽館・グループホームびえいの郷）。いずれも従業者数を事業所単位で確認できており、職員数の突合はこの方法によることが実証された。注5）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
+          <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.18（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）公表画面は3事業所分を受領した（グループホームファミリー・さわやか東神楽館・グループホームびえいの郷）。いずれも従業者数を事業所単位で確認できており、職員数の突合はこの方法によることが実証された。注5）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -1858,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1878,7 +1878,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>公表システムのオープンデータには従業者数が含まれないため、個別事業所の公表画面が従業者数の唯一の出所である。令和8年8月5日にグループホームファミリーの公表画面を受領し、定員と従業者数を確認した。同じくグループホームくるみの郷を探したが、公表システムに掲載が見つからなかった。</t>
+          <t>公表システムのオープンデータには従業者数が含まれないため、個別事業所の公表画面が従業者数の唯一の出所である。令和8年8月5日にグループホームファミリー、さわやか東神楽館及びグループホームびえいの郷の公表画面を、同月6日に居宅介護支援事業所おうかの公表画面を受領した。同じくグループホームくるみの郷を探したが、公表システムに掲載が見つからなかった。</t>
         </is>
       </c>
     </row>
@@ -2766,19 +2766,347 @@
       </c>
       <c r="E57" s="23" t="n"/>
     </row>
-    <row r="59" ht="130" customHeight="1">
+    <row r="59" ht="143" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.18（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）公表画面は3事業所分を受領した（グループホームファミリー・さわやか東神楽館・グループホームびえいの郷）。いずれも従業者数を事業所単位で確認できており、職員数の突合はこの方法によることが実証された。注5）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
+          <t>注1）認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。したがって、くるみの郷の定員・休止の状況は発注者自身が保有している。受託者が公表データから探すよりも、資料依頼No.18（指定事業所台帳）に含めてご提供いただくのが確実である。注2）上記の「考えられること」は受託者の推論であり、確かめたものではない。計画本文には用いない。注3）令和8年8月5日に受領した資料のうち、みんなの介護（民間の情報サイト）の「グループホーム ファミリー」は、旭川市永山1条11-2-38の同名の別施設（有限会社シャイニング・定員9人）である。区域内のグループホームファミリー（東川町北町5丁目・定員18人）とは別のものであるため、混同しないよう留意する。また同サイトは二次情報であり、本業務では出典に用いない。注4）公表画面は4事業所分を受領した（グループホームファミリー・さわやか東神楽館・グループホームびえいの郷・居宅介護支援事業所おうか）。いずれも従業者数を事業所単位で確認できており、職員数の突合はこの方法によることが実証された。注5）本シートにより、区域内のグループホームの定員は調査の5事業所81人にファミリー18人を加えて99人となった。残るのはくるみの郷1事業所のみである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>【居宅介護支援事業所 おうか（東川町）】公表画面　記入日 2026-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>事業開始年月日</t>
+        </is>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="23" t="n"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>調査の基準日（令和7年4月1日）より後である</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>指定年月日</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="23" t="n"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>見える化K3s（令和6年度10事業所）に含まれない。名簿13事業所との差3のうち1事業所がこれである</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>事業所番号</t>
+        </is>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>0173100694</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="n"/>
+      <c r="D64" s="23" t="n"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>北海道の指定事業所一覧と一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>サービス提供地域</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>東川町、東神楽町、美瑛町、旭川市</t>
+        </is>
+      </c>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="23" t="n"/>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>北海道の指定事業所一覧の通常の事業実施地域と一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>総従業者数</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>1人</t>
+        </is>
+      </c>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="23" t="n"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>介護支援専門員1人（常勤・兼務）のみ。専従は0人である</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>うち主任介護支援専門員</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>1人</t>
+        </is>
+      </c>
+      <c r="C67" s="22" t="n"/>
+      <c r="D67" s="23" t="n"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>管理者が主任介護支援専門員であり、他の職務と兼務している</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>前年度の採用者数・退職者数</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>いずれも0人</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>新規事業所であるため</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別利用者数</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>14人</t>
+        </is>
+      </c>
+      <c r="C69" s="22" t="n"/>
+      <c r="D69" s="23" t="n"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>要支援1〜要介護1が8人（57.1％）。内訳は要支援1が3人、要支援2が2人、要介護1が3人、要介護2が1人、要介護3が1人、要介護5が4人である</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>介護支援専門員1人当たりの利用者数</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>44人</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="n"/>
+      <c r="D70" s="23" t="n"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別利用者数の合計14人と整合しない。公表画面の内部で一致しないため、要介護度別の内訳のみを用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>【同一法人・同一所在地の4事業所（株式会社 龍空）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>事業所</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>出所</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>調査への回答</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>サービス付き高齢者向け住宅 桜華</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>サービス付き高齢者向け住宅（36戸）</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>北海道 住所地特例適用施設一覧（令和8年6月30日現在）</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>区域内のサービス付き高齢者向け住宅2件のうちの1件である。居所変更実態調査に回答したのは「サービス付き高齢者住宅ゆう」（30戸）のみであり、桜華は未回答である</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援事業所 おうか</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>北海道 介護保険事業所一覧、公表システムの個別画面</t>
+        </is>
+      </c>
+      <c r="D75" s="25" t="inlineStr">
+        <is>
+          <t>提出あり（全項目0）</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査の事業所票を受領しているが、指定が令和7年10月1日であり基準日に未開設のため集計対象から除く（点検事項No.7・解消）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>北海道 介護保険事業所一覧（令和8年6月30日現在）</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>区域内の訪問介護13事業所のうちの1つ。介護人材実態調査の訪問系の回答3事業所（シルバーハウス・花時計・フラワー）に含まれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>北海道 介護保険事業所一覧（令和8年6月30日現在）</t>
+        </is>
+      </c>
+      <c r="D77" s="25" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査の訪問系は訪問介護13事業所を母数としており、訪問看護は対象としていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="104" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>注1）「桜華」（おうか）は株式会社龍空が東川町西町8丁目5番23号で運営する事業所群の名称である。居宅介護支援のみ「おうか」とひらがなで登録されている。注2）サービス付き高齢者向け住宅 桜華は、北海道保健福祉部の住所地特例適用施設一覧（サービス付き高齢者向け住宅・令和8年6月30日現在）に36戸として掲載されており、区域内のサービス付き高齢者向け住宅の戸数66戸（ゆう30戸＋桜華36戸）に既に算入している（04シート）。届出済有料老人ホーム一覧には掲載がない。注3）居宅介護支援事業所おうかは居宅介護支援の指定であり、サービス付き高齢者向け住宅ではない。両者は同一の所在地にあるが別の事業である。注4）訪問介護事業所 桜華の指定年月日は確認できていない。居宅介護支援事業所おうかと同時期（令和7年10月）であれば、介護人材実態調査の基準日（令和7年4月1日）に未開設であり、未回答は当然ということになる。訪問介護事業所 桜華の公表画面により確認できる。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="62">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B17:D17"/>
@@ -2786,7 +3114,10 @@
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B56:C56"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="A79:E79"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
@@ -2796,18 +3127,23 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
@@ -2818,9 +3154,12 @@
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="D55:E55"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B39:D39"/>
@@ -6263,7 +6602,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>名簿が3多い。この間に開設した事業所があると考えられる。在宅生活改善調査の事業所票は居宅介護支援10事業所から受領しており、母数が10か13かで回収率の評価が変わる</t>
+          <t>名簿が3多い。うち1事業所（居宅介護支援事業所おうか）は令和7年10月1日指定であることを公表画面で確認した（10シート）。在宅生活改善調査の事業所票は居宅介護支援10事業所から受領しており、未回答は3事業所（ひがしかわ介護相談センター・ほの香・ライフデザイン陽風）である</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_通常の事業の実施地域" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_特別養護老人ホームの定員" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公表システムの個別画面による確認" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_訪問系の調査と公表画面の突合" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3169,6 +3170,801 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>訪問系3事業所の介護人材実態調査と公表画面の突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年8月6日に、訪問介護3事業所及び訪問看護1事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>【1　介護職員（訪問介護員等）の人数】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>事業所</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>調査
+R7.4.1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>公表画面
+記入日</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>花時計訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>実人数</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>16人</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>16人（2025-10-16）</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>13人（2025-10-16）</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>3人</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>3人（2025-10-16）</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>常勤換算</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>12.2人</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>調査は実人数で回答されており、常勤換算ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ヘルパーステーションフラワー</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>実人数</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>13人（2025-10-29）</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>8人</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>8人（2025-10-29）</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>5人</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>5人（2025-10-29）</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>常勤換算</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>9.3人</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>調査は実人数で回答されており、常勤換算ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>実人数</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>17人（2025-11-06）</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が4人多い。記入日は調査の約7か月後である</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>9人</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>11人（2025-11-06）</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が2人多い。記入日は調査の約7か月後である</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>4人</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>6人（2025-11-06）</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が2人多い。記入日は調査の約7か月後である</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>常勤換算</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>13.1人</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>調査は実人数で回答されており、常勤換算ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>【2　採用者数・離職者数】</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>事業所</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>調査
+過去1年間</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>公表画面
+前年度</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>花時計訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>採用者数</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>5人</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>1人</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>調査と公表画面で差がある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>離職（退職）者数</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>3人</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>調査と公表画面で差がある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>ヘルパーステーションフラワー</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>採用者数</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>7人</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>7人</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>離職（退職）者数</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>採用者数</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>3人</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>調査と公表画面で差がある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>離職（退職）者数</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>2人</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>【3　点検事項No.1（有料老人ホーム華とフラワーの重複）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>介護職員</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>採用／離職</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>調査　有料老人ホーム華（施設・通所系の票）</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>8人</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>5人</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>採用7人／離職2人</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>訪問系の票と同一の数値が記入されている。自由回答の文面も同一である（点検事項No.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>調査　ヘルパーステーションフラワー（訪問系の票）</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>8人</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>5人</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>採用7人／離職2人</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>公表画面　ヘルパーステーションフラワー（記入日 2025-10-29）</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>8人</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>5人</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>採用7人／退職2人</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>調査の訪問系の票と実人数・常勤・非常勤・採用・離職のすべてが一致する。訪問介護事業所の側の13人が実在の値であることが確認された</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="130" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -1879,7 +1879,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>公表システムのオープンデータには従業者数が含まれないため、個別事業所の公表画面が従業者数の唯一の出所である。令和8年8月5日にグループホームファミリー、さわやか東神楽館及びグループホームびえいの郷の公表画面を、同月6日に居宅介護支援事業所おうかの公表画面を受領した。同じくグループホームくるみの郷を探したが、公表システムに掲載が見つからなかった。</t>
+          <t>公表システムのオープンデータには従業者数が含まれないため、個別事業所の公表画面が従業者数の唯一の出所である。令和8年8月5日にグループホームファミリー、さわやか東神楽館及びグループホームびえいの郷の公表画面を、同月6日に居宅介護支援事業所おうか、訪問介護3事業所及び訪問看護1事業所の公表画面を、続いて調査未回答の訪問介護2事業所（ケンセイシャレバレッジ・東神楽町ホームヘルプサービスセンター）の公表画面を受領した（受領は計10事業所）。訪問系の突合は11のシートに示す。同じくグループホームくるみの郷を探したが、公表システムに掲載が見つからなかった。</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3190,14 +3190,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>訪問系3事業所の介護人材実態調査と公表画面の突合</t>
+          <t>訪問介護事業所の介護人材実態調査と公表画面の突合</t>
         </is>
       </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年8月6日に、訪問介護3事業所及び訪問看護1事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合する。</t>
+          <t>令和8年8月6日に訪問介護3事業所及び訪問看護1事業所の、同月中に調査未回答の訪問介護2事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合したうえで、未回答事業所を公表画面のみで把握した結果を併せて示す。</t>
         </is>
       </c>
     </row>
@@ -3946,20 +3946,608 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="130" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。</t>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>【4　調査未回答の事業所の公表画面による把握】</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>事業所</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>記入日</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>実人数</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>常勤／非常勤</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>常勤換算</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>把握できた事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>指定（介護予防）訪問介護ケンセイシャレバレッジ</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>10人</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>6人／4人</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>4.0人</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>採用1人・退職0人、介護福祉士（延べ）7人、経験年数10年以上40.0％、利用者11人（前年同月10人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>6人</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>4人／2人</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>6.0人</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>採用0人・退職2人、介護福祉士（延べ）6人、経験年数10年以上83.3％、利用者19人（前年同月18人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>【5　訪問介護13事業所の把握の状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>事業所</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>調査</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>公表画面</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>実人数</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>花時計訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>16人</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>調査と公表画面が一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>6人</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>10人</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所ひばり</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 ほがらか</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>東川町社協訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護ステーション ゆう</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>ヘルパーステーション フラワー</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>調査と公表画面が一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手。同一法人の居宅介護支援事業所おうかは令和7年10月1日の指定であり、当事業所の指定年月日の確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所 恩送り</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>17人</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が調査より4人多い</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="14" t="inlineStr"/>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>把握できた事業所の計</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>5／13事業所</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>62人</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>訪問介護13事業所のうち5事業所（38.5％）について訪問介護員等の実人数を把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="234" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。注6）調査未回答の2事業所（ケンセイシャレバレッジ・東神楽町ホームヘルプサービスセンター）は、公表画面が訪問介護員等の人数の唯一の出所である。いずれも調査の基準日（令和7年4月1日）より前からの指定であり（平成22年5月1日・平成12年4月1日）、基準日に開設していなかったことによる未回答ではない。注7）両事業所の訪問介護員等は、常勤・非常勤ともすべて兼務である。ケンセイシャレバレッジは実人数10人に対し常勤換算4.0人、東神楽町ホームヘルプサービスセンターは実人数6人に対し常勤換算6.0人で、実人数と常勤換算の比が事業所により大きく異なる。訪問系の従事者数を実人数で積み上げる場合は、この点を明記のうえ用いる。注8）ケンセイシャレバレッジの所在地は、北海道の指定事業所一覧では「北二条西3丁目254番地49」、公表画面及び公表システムの位置情報付きデータでは「北2条西3丁目254番73号」であり一致しない。移転か一覧の誤りかは確認していない。注9）残る未把握は8事業所である。公表画面を追加で入手できれば、訪問介護13事業所すべての訪問介護員等の人数を把握でき、「訪問系3／13事業所」という代表性の限界が解消する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -256,6 +256,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3176,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3197,7 +3200,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年8月6日に訪問介護3事業所及び訪問看護1事業所の、同月中に調査未回答の訪問介護2事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合したうえで、未回答事業所を公表画面のみで把握した結果を併せて示す。</t>
+          <t>令和8年8月6日に訪問介護3事業所及び訪問看護1事業所の、同月中に調査未回答の訪問介護3事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合したうえで、未回答事業所を公表画面のみで把握した結果を併せて示す。</t>
         </is>
       </c>
     </row>
@@ -4049,74 +4052,74 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所ひばり</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>12人</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>11人／1人</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>6.3人</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>採用0人・退職1人、介護福祉士（延べ）5人、経験年数10年以上41.7％、利用者25人（前年同月22人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>【5　訪問介護13事業所の把握の状況】</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>事業所</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>調査</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>公表画面</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>実人数</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>花時計訪問介護事業所</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="E41" s="20" t="inlineStr">
-        <is>
-          <t>16人</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>調査と公表画面が一致する</t>
         </is>
       </c>
     </row>
@@ -4128,27 +4131,27 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>東神楽町ホームヘルプサービスセンター</t>
+          <t>花時計訪問介護事業所</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>回答</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>6人</t>
+          <t>16人</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した</t>
+          <t>調査と公表画面が一致する</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4163,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
+          <t>東神楽町ホームヘルプサービスセンター</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -4170,12 +4173,12 @@
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>10人</t>
+          <t>6人</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -4192,7 +4195,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護事業所ひばり</t>
+          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -4200,19 +4203,19 @@
           <t>未回答</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>10人</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4227,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>訪問介護事業所 ほがらか</t>
+          <t>指定訪問介護事業所ひばり</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -4232,31 +4235,31 @@
           <t>未回答</t>
         </is>
       </c>
-      <c r="D45" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>12人</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面のみで把握した。12人中11人が兼務である</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>東川町社協訪問介護事業所</t>
+          <t>訪問介護事業所 ほがらか</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -4288,7 +4291,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護ステーション ゆう</t>
+          <t>東川町社協訪問介護事業所</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -4320,7 +4323,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+          <t>指定訪問介護ステーション ゆう</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4352,27 +4355,27 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>ヘルパーステーション フラワー</t>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>回答</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>13人</t>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>調査と公表画面が一致する</t>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
         </is>
       </c>
     </row>
@@ -4384,27 +4387,27 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>訪問介護事業所 桜華</t>
+          <t>ヘルパーステーション フラワー</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>未回答</t>
-        </is>
-      </c>
-      <c r="D50" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手。同一法人の居宅介護支援事業所おうかは令和7年10月1日の指定であり、当事業所の指定年月日の確認を要する</t>
+          <t>調査と公表画面が一致する</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4419,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護事業所 恩送り</t>
+          <t>訪問介護事業所 桜華</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4436,19 +4439,19 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面が未入手。同一法人の居宅介護支援事業所おうかは令和7年10月1日の指定であり、当事業所の指定年月日の確認を要する</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>東川町</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>美瑛町ホームヘルプサービスセンター</t>
+          <t>指定訪問介護事業所 恩送り</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -4480,74 +4483,242 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
           <t>シルバーハウス訪問介護事業所</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
-      <c r="D53" s="24" t="inlineStr">
+      <c r="D54" s="24" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E54" s="20" t="inlineStr">
         <is>
           <t>17人</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>公表画面が調査より4人多い</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="14" t="inlineStr"/>
-      <c r="B54" s="28" t="inlineStr">
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="14" t="inlineStr"/>
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>把握できた事業所の計</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>5／13事業所</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>62人</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
-        <is>
-          <t>訪問介護13事業所のうち5事業所（38.5％）について訪問介護員等の実人数を把握した</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="234" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。注6）調査未回答の2事業所（ケンセイシャレバレッジ・東神楽町ホームヘルプサービスセンター）は、公表画面が訪問介護員等の人数の唯一の出所である。いずれも調査の基準日（令和7年4月1日）より前からの指定であり（平成22年5月1日・平成12年4月1日）、基準日に開設していなかったことによる未回答ではない。注7）両事業所の訪問介護員等は、常勤・非常勤ともすべて兼務である。ケンセイシャレバレッジは実人数10人に対し常勤換算4.0人、東神楽町ホームヘルプサービスセンターは実人数6人に対し常勤換算6.0人で、実人数と常勤換算の比が事業所により大きく異なる。訪問系の従事者数を実人数で積み上げる場合は、この点を明記のうえ用いる。注8）ケンセイシャレバレッジの所在地は、北海道の指定事業所一覧では「北二条西3丁目254番地49」、公表画面及び公表システムの位置情報付きデータでは「北2条西3丁目254番73号」であり一致しない。移転か一覧の誤りかは確認していない。注9）残る未把握は8事業所である。公表画面を追加で入手できれば、訪問介護13事業所すべての訪問介護員等の人数を把握でき、「訪問系3／13事業所」という代表性の限界が解消する。</t>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>6／13事業所</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>74人</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>訪問介護13事業所のうち6事業所（46.2％）について訪問介護員等の実人数を把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>【6　同一敷地に住宅型有料老人ホームがある訪問介護事業所】</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>法人・敷地</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>施設側（調査）</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>訪問介護側</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>採用／離職</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="52" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホーム華／ヘルパーステーションフラワー（有限会社フラワー・東川町）</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>13人（常勤8・非常勤5）</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>13人（常勤8・非常勤5）</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>調査 採用7・離職2／公表 採用7・退職2</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>完全に一致</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>施設票と訪問系の票に同一の数値が記入されている（点検事項No.1）。公表画面は訪問介護側の13人が実在の値であることを裏づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="52" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームひばりの森／指定訪問介護事業所ひばり（株式会社オレンジサポート・東神楽町）</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>9人（常勤7・非常勤2）</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>12人（常勤11・非常勤1）</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>調査 採用3・離職0／公表 採用0・退職1</t>
+        </is>
+      </c>
+      <c r="E60" s="25" t="inlineStr">
+        <is>
+          <t>一致しない</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>施設票の9人と訪問介護の12人は別の数値であり、同一の値の転記ではない。ただし訪問介護12人のうち11人が兼務であり、同一法人のグループホームひばり（調査21人）及びひばりの森（調査9人）との重複の有無は確かめられていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="52" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム花時計／花時計訪問介護事業所（医療法人回生会・東神楽町）</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>施設票の提出なし</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>16人（常勤13・非常勤3）</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>調査 採用5・離職3／公表 採用1・退職2</t>
+        </is>
+      </c>
+      <c r="E61" s="30" t="inlineStr">
+        <is>
+          <t>施設側の回答なし</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム花時計からの施設票がないため、重複の問題は生じない</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="273" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。注6）調査未回答の3事業所（ケンセイシャレバレッジ・東神楽町ホームヘルプサービスセンター・ひばり）は、公表画面が訪問介護員等の人数の唯一の出所である。いずれも調査の基準日（令和7年4月1日）より前からの指定であり（平成22年5月1日・平成12年4月1日・平成27年6月1日）、基準日に開設していなかったことによる未回答ではない。注7）3事業所とも訪問介護員等のほとんどが他のサービスとの兼務である（ケンセイシャレバレッジ10人中10人、東神楽町ホームヘルプサービスセンター6人中6人、ひばり12人中11人）。実人数に対する常勤換算は4.0人／10人、6.0人／6人、6.3人／12人で、比が事業所により大きく異なる。訪問系の従事者数を実人数で積み上げる場合は、この点を明記のうえ用いる。注7の2）ひばりは、同一敷地に住宅型有料老人ホームひばりの森（調査回答9人）とグループホームひばり（調査回答21人）があり、訪問介護12人との重複の有無は確かめられていない。点検事項No.1と同じ構造であるが、施設票と訪問介護の数値は一致しないため転記ではない（本シート6）。注8）ケンセイシャレバレッジの所在地は、北海道の指定事業所一覧では「北二条西3丁目254番地49」、公表画面及び公表システムの位置情報付きデータでは「北2条西3丁目254番73号」であり一致しない。移転か一覧の誤りかは確認していない。注9）残る未把握は7事業所である。公表画面を追加で入手できれば、訪問介護13事業所すべての訪問介護員等の人数を把握でき、「訪問系3／13事業所」という代表性の限界が解消する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,6 +259,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3179,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3200,7 +3203,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年8月6日に訪問介護3事業所及び訪問看護1事業所の、同月中に調査未回答の訪問介護3事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合したうえで、未回答事業所を公表画面のみで把握した結果を併せて示す。</t>
+          <t>令和8年8月6日以降に、訪問介護11事業所及び訪問看護1事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合したうえで、未回答8事業所を公表画面のみで把握した結果と、居住系の住まいとの併設の状況を併せて示す。</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3350,7 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>12.2人</t>
+          <t>12.20人</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -3463,7 +3466,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>9.3人</t>
+          <t>9.30人</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -3579,7 +3582,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>13.1人</t>
+          <t>13.10人</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -4011,7 +4014,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>4.0人</t>
+          <t>4.00人</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -4043,7 +4046,7 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>6.0人</t>
+          <t>6.00人</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -4075,7 +4078,7 @@
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>6.3人</t>
+          <t>6.30人</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -4084,246 +4087,246 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>6人／7人</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>6.40人</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>採用2人・退職2人、介護福祉士（延べ）6人、経験年数10年以上38.5％、利用者49人（前年同月43人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>東川町社協訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>7人</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>3人／4人</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>4.20人</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>採用0人・退職0人、介護福祉士（延べ）5人、経験年数10年以上14.3％、利用者16人（前年同月20人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>31人</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>11人／20人</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>8.28人</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>採用6人・退職10人、介護福祉士（延べ）17人、経験年数10年以上35.5％、利用者47人（前年同月48人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>22人</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>10人／12人</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>5.00人</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>採用0人・退職0人、介護福祉士（延べ）8人、経験年数10年以上63.6％、利用者25人（前年同月7人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所 恩送り</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>9人／2人</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>採用0人・退職0人、介護福祉士（延べ）9人、経験年数10年以上81.8％、利用者17人（前年同月0人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>【5　訪問介護13事業所の把握の状況】</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>事業所</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>調査</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>公表画面</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>実人数</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>花時計訪問介護事業所</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>16人</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>調査と公表画面が一致する</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町ホームヘルプサービスセンター</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>未回答</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="E43" s="20" t="inlineStr">
-        <is>
-          <t>6人</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>公表画面のみで把握した</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>未回答</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="E44" s="20" t="inlineStr">
-        <is>
-          <t>10人</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>公表画面のみで把握した</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>指定訪問介護事業所ひばり</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>未回答</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>12人</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>公表画面のみで把握した。12人中11人が兼務である</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>訪問介護事業所 ほがらか</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>未回答</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>東川町社協訪問介護事業所</t>
+          <t>花時計訪問介護事業所</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>未回答</t>
-        </is>
-      </c>
-      <c r="D47" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>16人</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>調査と公表画面が一致する</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護ステーション ゆう</t>
+          <t>東神楽町ホームヘルプサービスセンター</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4331,31 +4334,31 @@
           <t>未回答</t>
         </is>
       </c>
-      <c r="D48" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>6人</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -4363,63 +4366,63 @@
           <t>未回答</t>
         </is>
       </c>
-      <c r="D49" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>10人</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>ヘルパーステーション フラワー</t>
+          <t>指定訪問介護事業所ひばり</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>13人</t>
+          <t>12人</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>調査と公表画面が一致する</t>
+          <t>公表画面のみで把握した。12人中11人が兼務である</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>訪問介護事業所 桜華</t>
+          <t>訪問介護事業所 ほがらか</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4439,7 +4442,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手。同一法人の居宅介護支援事業所おうかは令和7年10月1日の指定であり、当事業所の指定年月日の確認を要する</t>
+          <t>公表画面が未入手であり、従事者数を把握できていない</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4454,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護事業所 恩送り</t>
+          <t>東川町社協訪問介護事業所</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -4459,31 +4462,31 @@
           <t>未回答</t>
         </is>
       </c>
-      <c r="D52" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>7人</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>東川町</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>美瑛町ホームヘルプサービスセンター</t>
+          <t>指定訪問介護ステーション ゆう</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4510,215 +4513,831 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>31人</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した。区域内で最多。退職10人</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>ヘルパーステーション フラワー</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>調査と公表画面が一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>22人</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した。指定は令和6年10月1日で基準日に開設済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所 恩送り</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した。常勤換算の記載がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>シルバーハウス訪問介護事業所</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D59" s="24" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="E54" s="20" t="inlineStr">
+      <c r="E59" s="20" t="inlineStr">
         <is>
           <t>17人</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>公表画面が調査より4人多い</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="14" t="inlineStr"/>
-      <c r="B55" s="28" t="inlineStr">
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="14" t="inlineStr"/>
+      <c r="B60" s="28" t="inlineStr">
         <is>
           <t>把握できた事業所の計</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>6／13事業所</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>74人</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
-        <is>
-          <t>訪問介護13事業所のうち6事業所（46.2％）について訪問介護員等の実人数を把握した</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>11／13事業所</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>158人</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>訪問介護13事業所のうち11事業所（84.6％）について訪問介護員等の実人数を把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>【6　同一敷地に住宅型有料老人ホームがある訪問介護事業所】</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>法人・敷地</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>施設側（調査）</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>訪問介護側</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>採用／離職</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>数値</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>見方</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="52" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="64" ht="52" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>有料老人ホーム華／ヘルパーステーションフラワー（有限会社フラワー・東川町）</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>13人（常勤8・非常勤5）</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>13人（常勤8・非常勤5）</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>調査 採用7・離職2／公表 採用7・退職2</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E64" s="24" t="inlineStr">
         <is>
           <t>完全に一致</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>施設票と訪問系の票に同一の数値が記入されている（点検事項No.1）。公表画面は訪問介護側の13人が実在の値であることを裏づける</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="52" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="65" ht="52" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>住宅型有料老人ホームひばりの森／指定訪問介護事業所ひばり（株式会社オレンジサポート・東神楽町）</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>9人（常勤7・非常勤2）</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>12人（常勤11・非常勤1）</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>調査 採用3・離職0／公表 採用0・退職1</t>
         </is>
       </c>
-      <c r="E60" s="25" t="inlineStr">
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>一致しない</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>施設票の9人と訪問介護の12人は別の数値であり、同一の値の転記ではない。ただし訪問介護12人のうち11人が兼務であり、同一法人のグループホームひばり（調査21人）及びひばりの森（調査9人）との重複の有無は確かめられていない</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="52" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="66" ht="52" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>住宅型有料老人ホーム花時計／花時計訪問介護事業所（医療法人回生会・東神楽町）</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>施設票の提出なし</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>16人（常勤13・非常勤3）</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>調査 採用5・離職3／公表 採用1・退職2</t>
         </is>
       </c>
-      <c r="E61" s="30" t="inlineStr">
+      <c r="E66" s="30" t="inlineStr">
         <is>
           <t>施設側の回答なし</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>住宅型有料老人ホーム花時計からの施設票がないため、重複の問題は生じない</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="273" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。注6）調査未回答の3事業所（ケンセイシャレバレッジ・東神楽町ホームヘルプサービスセンター・ひばり）は、公表画面が訪問介護員等の人数の唯一の出所である。いずれも調査の基準日（令和7年4月1日）より前からの指定であり（平成22年5月1日・平成12年4月1日・平成27年6月1日）、基準日に開設していなかったことによる未回答ではない。注7）3事業所とも訪問介護員等のほとんどが他のサービスとの兼務である（ケンセイシャレバレッジ10人中10人、東神楽町ホームヘルプサービスセンター6人中6人、ひばり12人中11人）。実人数に対する常勤換算は4.0人／10人、6.0人／6人、6.3人／12人で、比が事業所により大きく異なる。訪問系の従事者数を実人数で積み上げる場合は、この点を明記のうえ用いる。注7の2）ひばりは、同一敷地に住宅型有料老人ホームひばりの森（調査回答9人）とグループホームひばり（調査回答21人）があり、訪問介護12人との重複の有無は確かめられていない。点検事項No.1と同じ構造であるが、施設票と訪問介護の数値は一致しないため転記ではない（本シート6）。注8）ケンセイシャレバレッジの所在地は、北海道の指定事業所一覧では「北二条西3丁目254番地49」、公表画面及び公表システムの位置情報付きデータでは「北2条西3丁目254番73号」であり一致しない。移転か一覧の誤りかは確認していない。注9）残る未把握は7事業所である。公表画面を追加で入手できれば、訪問介護13事業所すべての訪問介護員等の人数を把握でき、「訪問系3／13事業所」という代表性の限界が解消する。</t>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>【7　訪問介護事業所と居住系の住まいとの併設の状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>事業所</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>訪問介護員等</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>利用者</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>併設する住まい</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>花時計訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>16人</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>23人</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム花時計（定員30）</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>公表画面の建物名の欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>17人</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>27人</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームびえいの郷</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>公表画面の建物名の欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>ヘルパーステーションフラワー</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>18人</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホーム華（住宅型）</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>公表画面の建物名の欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所ひばり</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>12人</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>25人</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームひばりの森（定員43）</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>公表画面の建物名の欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t>31人</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>47人</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム縁結び（定員22）</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>北海道の届出済有料老人ホーム一覧と所在地が一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>22人</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>25人</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>サービス付き高齢者向け住宅 桜華（36戸）</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>北海道の住所地特例適用施設一覧と所在地が一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所 恩送り</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>17人</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム恩送り（定員25）</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>公表画面の特色の欄に「有料老人ホーム併設の介護事業所であり、主に施設内での介護サービスを提供している」との記載がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>指定（介護予防）訪問介護ケンセイシャレバレッジ</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>10人</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>法人は住宅型有料老人ホームひがしかぐらふらわーはうす（定員18）を運営するが、訪問介護事業所とは所在地が異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>6人</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>19人</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>49人</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>東川町社協訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>7人</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>16人</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>併設7事業所</t>
+        </is>
+      </c>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>122人</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>182人</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>把握できた訪問介護員等158人の77.2％、利用者277人の65.7％を併設の事業所が占める</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>併設なし4事業所</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>36人</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>95人</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>社会福祉協議会3事業所とケンセイシャレバレッジである</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="377" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。注6）調査未回答の8事業所は、公表画面が訪問介護員等の人数の唯一の出所である。8事業所すべてが調査の基準日（令和7年4月1日）より前からの指定であり、基準日に開設していなかったことによる未回答ではない。訪問介護事業所 桜華の指定は令和6年10月1日であり、同一法人の居宅介護支援事業所おうか（令和7年10月1日指定）とは1年の差がある。桜華は基準日に開設していた。注7）実人数に対する常勤換算の比は事業所により大きく異なる（東神楽町ホームヘルプサービスセンター6.0人／6人に対し、縁結び8.28人／31人）。兼務の多寡によるものである。訪問系の従事者数を実人数で積み上げる場合は、この点を明記のうえ用いる。注7の2）ひばりは、同一敷地に住宅型有料老人ホームひばりの森（調査回答9人）とグループホームひばり（調査回答21人）があり、訪問介護12人との重複の有無は確かめられていない。点検事項No.1と同じ構造であるが、施設票と訪問介護の数値は一致しないため転記ではない（本シート6）。注7の3）恩送りは常勤換算人数及び訪問介護員等1人当たりのサービス提供時間の欄がいずれも0であり、利用者17人・提供時間20時間との整合がとれない。記入漏れとみられるため、常勤換算は用いない。注7の4）美瑛町ホームヘルプサービスセンターは常勤の週の勤務すべき時間数が38.75時間であり、他の10事業所（40時間）と異なる。常勤換算の水準を事業所間で比べる際に留意する。注8）ケンセイシャレバレッジの所在地は、北海道の指定事業所一覧では「北二条西3丁目254番地49」、公表画面及び公表システムの位置情報付きデータでは「北2条西3丁目254番73号」であり一致しない。移転か一覧の誤りかは確認していない。注9）残る未把握は訪問介護事業所 ほがらか（東神楽町）及び指定訪問介護ステーション ゆう（東川町）の2事業所である。この2事業所の公表画面を入手すれば、訪問介護13事業所すべての訪問介護員等の人数を把握でき、「訪問系3／13事業所」という代表性の限界が完全に解消する。注10）本シート7のとおり、把握できた訪問介護員等158人のうち122人（77.2％）が、住宅型有料老人ホーム又はサービス付き高齢者向け住宅に併設された事業所に所属している。利用者277人のうち182人（65.7％）も同様である。区域内の訪問介護は、居宅で暮らす方に対する訪問よりも、居住系の住まいの入居者に対する訪問が主となっている。第4章の在宅サービスの見込量において訪問介護を「在宅」として一括して扱うと、実態と離れた読み方につながる。見込量の算定には見える化D系列の受給者数を用いるため算定そのものへの影響はないが、本文の記述では併設の割合を明記する。併設なしの4事業所は、3町の社会福祉協議会が運営する3事業所とケンセイシャレバレッジであり、訪問介護員等は36人にとどまる。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A62:F62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -3182,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3203,7 +3203,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年8月6日以降に、訪問介護11事業所及び訪問看護1事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、その3事業所すべてについて公表画面が揃った。調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合したうえで、未回答8事業所を公表画面のみで把握した結果と、居住系の住まいとの併設の状況を併せて示す。</t>
+          <t>令和8年8月6日以降に、区域内の訪問介護13事業所すべて及び訪問看護1事業所の介護サービス情報公表システムの個別公表画面を受領した。介護人材実態調査の訪問系は13事業所のうち3事業所からの回答であり、調査（令和7年4月1日現在）と公表画面（令和7年10〜11月記入）を突合したうえで、未回答10事業所を公表画面のみで把握した結果と、居住系の住まいとの併設の状況を併せて示す。これにより訪問介護員等181人の全数が把握できた。</t>
         </is>
       </c>
     </row>
@@ -4247,106 +4247,106 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 ほがらか</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>17人</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>10人／7人</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>5.60人</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>採用2人・退職6人、介護福祉士（延べ）14人、経験年数10年以上88.2％、利用者26人（前年同月17人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護ステーションゆう</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>6人</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>5人／1人</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>6.00人</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>採用1人・退職1人、介護福祉士（延べ）1人、経験年数10年以上66.7％、利用者43人（前年同月39人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>【5　訪問介護13事業所の把握の状況】</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>事業所</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>調査</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>公表画面</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>実人数</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>花時計訪問介護事業所</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>16人</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>調査と公表画面が一致する</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町ホームヘルプサービスセンター</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>未回答</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="E48" s="20" t="inlineStr">
-        <is>
-          <t>6人</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
@@ -4358,27 +4358,27 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
+          <t>花時計訪問介護事業所</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>回答</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>10人</t>
+          <t>16人</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した</t>
+          <t>調査と公表画面が一致する</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護事業所ひばり</t>
+          <t>東神楽町ホームヘルプサービスセンター</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -4400,17 +4400,17 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>12人</t>
+          <t>6人</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した。12人中11人が兼務である</t>
+          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>訪問介護事業所 ほがらか</t>
+          <t>指定（介護予防）訪問介護事業所 ケンセイシャレバレッジ</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4430,31 +4430,31 @@
           <t>未回答</t>
         </is>
       </c>
-      <c r="D51" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>10人</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>東川町社協訪問介護事業所</t>
+          <t>指定訪問介護事業所ひばり</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -4464,29 +4464,29 @@
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>7人</t>
+          <t>12人</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した</t>
+          <t>公表画面のみで把握した。12人中11人が兼務である</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護ステーション ゆう</t>
+          <t>訪問介護事業所 ほがらか</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4494,19 +4494,19 @@
           <t>未回答</t>
         </is>
       </c>
-      <c r="D53" s="26" t="inlineStr">
-        <is>
-          <t>未入手</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>17人</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>公表画面が未入手であり、従事者数を把握できていない</t>
+          <t>公表画面のみで把握した。退職6人が採用2人を上回る</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+          <t>東川町社協訪問介護事業所</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -4528,17 +4528,17 @@
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>31人</t>
+          <t>7人</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した。区域内で最多。退職10人</t>
+          <t>公表画面のみで把握した</t>
         </is>
       </c>
     </row>
@@ -4550,27 +4550,27 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ヘルパーステーション フラワー</t>
+          <t>指定訪問介護ステーション ゆう</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
-          <t>13人</t>
+          <t>6人</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>調査と公表画面が一致する</t>
+          <t>公表画面のみで把握した。6人で利用者43人を担当する</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>訪問介護事業所 桜華</t>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4592,17 +4592,17 @@
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>22人</t>
+          <t>31人</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した。指定は令和6年10月1日で基準日に開設済み</t>
+          <t>公表画面のみで把握した。区域内で最多。退職10人</t>
         </is>
       </c>
     </row>
@@ -4614,39 +4614,39 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護事業所 恩送り</t>
+          <t>ヘルパーステーション フラワー</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>回答</t>
         </is>
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>11人</t>
+          <t>13人</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した。常勤換算の記載がない</t>
+          <t>調査と公表画面が一致する</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>東川町</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>美瑛町ホームヘルプサービスセンター</t>
+          <t>訪問介護事業所 桜華</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4656,347 +4656,347 @@
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>13人</t>
+          <t>22人</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>公表画面のみで把握した</t>
+          <t>公表画面のみで把握した。指定は令和6年10月1日で基準日に開設済み</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>指定訪問介護事業所 恩送り</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した。常勤換算の記載がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>公表画面のみで把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>シルバーハウス訪問介護事業所</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D61" s="24" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="E61" s="20" t="inlineStr">
         <is>
           <t>17人</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>公表画面が調査より4人多い</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="14" t="inlineStr"/>
-      <c r="B60" s="28" t="inlineStr">
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="14" t="inlineStr"/>
+      <c r="B62" s="28" t="inlineStr">
         <is>
           <t>把握できた事業所の計</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>11／13事業所</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>158人</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>訪問介護13事業所のうち11事業所（84.6％）について訪問介護員等の実人数を把握した</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>13／13事業所</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>181人</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>訪問介護13事業所のうち13事業所（100.0％）について訪問介護員等の実人数を把握した</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>【6　同一敷地に住宅型有料老人ホームがある訪問介護事業所】</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>法人・敷地</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>施設側（調査）</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>訪問介護側</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>採用／離職</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>数値</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="52" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>有料老人ホーム華／ヘルパーステーションフラワー（有限会社フラワー・東川町）</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>13人（常勤8・非常勤5）</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>13人（常勤8・非常勤5）</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>調査 採用7・離職2／公表 採用7・退職2</t>
-        </is>
-      </c>
-      <c r="E64" s="24" t="inlineStr">
-        <is>
-          <t>完全に一致</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>施設票と訪問系の票に同一の数値が記入されている（点検事項No.1）。公表画面は訪問介護側の13人が実在の値であることを裏づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="52" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ホームひばりの森／指定訪問介護事業所ひばり（株式会社オレンジサポート・東神楽町）</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>9人（常勤7・非常勤2）</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>12人（常勤11・非常勤1）</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>調査 採用3・離職0／公表 採用0・退職1</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
-        <is>
-          <t>一致しない</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>施設票の9人と訪問介護の12人は別の数値であり、同一の値の転記ではない。ただし訪問介護12人のうち11人が兼務であり、同一法人のグループホームひばり（調査21人）及びひばりの森（調査9人）との重複の有無は確かめられていない</t>
         </is>
       </c>
     </row>
     <row r="66" ht="52" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
+          <t>有料老人ホーム華／ヘルパーステーションフラワー（有限会社フラワー・東川町）</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>13人（常勤8・非常勤5）</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>13人（常勤8・非常勤5）</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>調査 採用7・離職2／公表 採用7・退職2</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>完全に一致</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>施設票と訪問系の票に同一の数値が記入されている（点検事項No.1）。公表画面は訪問介護側の13人が実在の値であることを裏づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームひばりの森／指定訪問介護事業所ひばり（株式会社オレンジサポート・東神楽町）</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>9人（常勤7・非常勤2）</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>12人（常勤11・非常勤1）</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>調査 採用3・離職0／公表 採用0・退職1</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
+        <is>
+          <t>一致しない</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>施設票の9人と訪問介護の12人は別の数値であり、同一の値の転記ではない。ただし訪問介護12人のうち11人が兼務であり、同一法人のグループホームひばり（調査21人）及びひばりの森（調査9人）との重複の有無は確かめられていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="52" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホームゆう・サ高住ゆう・グループホームゆう／訪問介護ステーションゆう（株式会社栄友・東川町）</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>有料8人・サ高住0人・GH16人・デイ7人</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>6人（常勤5・非常勤1）</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>調査 記載なし／公表 採用1・退職1</t>
+        </is>
+      </c>
+      <c r="E68" s="25" t="inlineStr">
+        <is>
+          <t>施設票と別</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>同一敷地の4施設から調査に回答があるが、訪問介護事業所からの回答はない。訪問介護6人が施設票の職員と重複するかは確かめられていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="52" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>住宅型有料老人ホーム花時計／花時計訪問介護事業所（医療法人回生会・東神楽町）</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>施設票の提出なし</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>16人（常勤13・非常勤3）</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>調査 採用5・離職3／公表 採用1・退職2</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>施設側の回答なし</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>住宅型有料老人ホーム花時計からの施設票がないため、重複の問題は生じない</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>【7　訪問介護事業所と居住系の住まいとの併設の状況】</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>事業所</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>訪問介護員等</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>利用者</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>併設する住まい</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>併設</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>花時計訪問介護事業所</t>
-        </is>
-      </c>
-      <c r="C70" s="19" t="inlineStr">
-        <is>
-          <t>16人</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>23人</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ホーム花時計（定員30）</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>公表画面の建物名の欄</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>併設</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>シルバーハウス訪問介護事業所</t>
-        </is>
-      </c>
-      <c r="C71" s="19" t="inlineStr">
-        <is>
-          <t>17人</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>27人</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>住宅型有料老人ホームびえいの郷</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>公表画面の建物名の欄</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>併設</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>ヘルパーステーションフラワー</t>
-        </is>
-      </c>
-      <c r="C72" s="19" t="inlineStr">
-        <is>
-          <t>13人</t>
-        </is>
-      </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>18人</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>有料老人ホーム華（住宅型）</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>公表画面の建物名の欄</t>
         </is>
       </c>
     </row>
@@ -5008,22 +5008,22 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護事業所ひばり</t>
+          <t>花時計訪問介護事業所</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>12人</t>
+          <t>16人</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>25人</t>
+          <t>23人</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ホームひばりの森（定員43）</t>
+          <t>住宅型有料老人ホーム花時計（定員30）</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -5040,27 +5040,27 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+          <t>シルバーハウス訪問介護事業所</t>
         </is>
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>31人</t>
+          <t>17人</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>47人</t>
+          <t>27人</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ホーム縁結び（定員22）</t>
+          <t>住宅型有料老人ホームびえいの郷</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>北海道の届出済有料老人ホーム一覧と所在地が一致する</t>
+          <t>公表画面の建物名の欄</t>
         </is>
       </c>
     </row>
@@ -5072,27 +5072,27 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>訪問介護事業所 桜華</t>
+          <t>ヘルパーステーションフラワー</t>
         </is>
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>22人</t>
+          <t>13人</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>25人</t>
+          <t>18人</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>サービス付き高齢者向け住宅 桜華（36戸）</t>
+          <t>有料老人ホーム華（住宅型）</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>北海道の住所地特例適用施設一覧と所在地が一致する</t>
+          <t>公表画面の建物名の欄</t>
         </is>
       </c>
     </row>
@@ -5104,240 +5104,400 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>指定訪問介護事業所 恩送り</t>
+          <t>指定訪問介護事業所ひばり</t>
         </is>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>11人</t>
+          <t>12人</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>17人</t>
+          <t>25人</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ホーム恩送り（定員25）</t>
+          <t>住宅型有料老人ホームひばりの森（定員43）</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>公表画面の特色の欄に「有料老人ホーム併設の介護事業所であり、主に施設内での介護サービスを提供している」との記載がある</t>
+          <t>公表画面の建物名の欄</t>
         </is>
       </c>
     </row>
     <row r="77" ht="32" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>併設なし</t>
+          <t>併設</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>指定（介護予防）訪問介護ケンセイシャレバレッジ</t>
-        </is>
-      </c>
-      <c r="C77" s="20" t="inlineStr">
-        <is>
-          <t>10人</t>
+          <t>指定訪問介護（指定介護予防訪問介護）事業所 縁結び</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>31人</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>11人</t>
+          <t>47人</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>住宅型有料老人ホーム縁結び（定員22）</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>法人は住宅型有料老人ホームひがしかぐらふらわーはうす（定員18）を運営するが、訪問介護事業所とは所在地が異なる</t>
+          <t>北海道の届出済有料老人ホーム一覧と所在地が一致する</t>
         </is>
       </c>
     </row>
     <row r="78" ht="32" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>併設なし</t>
+          <t>併設</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>東神楽町ホームヘルプサービスセンター</t>
-        </is>
-      </c>
-      <c r="C78" s="20" t="inlineStr">
-        <is>
-          <t>6人</t>
+          <t>訪問介護事業所 桜華</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>22人</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>19人</t>
+          <t>25人</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>サービス付き高齢者向け住宅 桜華（36戸）</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
+          <t>北海道の住所地特例適用施設一覧と所在地が一致する</t>
         </is>
       </c>
     </row>
     <row r="79" ht="32" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>併設なし</t>
+          <t>併設</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>美瑛町ホームヘルプサービスセンター</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="inlineStr">
-        <is>
-          <t>13人</t>
+          <t>指定訪問介護事業所 恩送り</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>11人</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>49人</t>
+          <t>17人</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>住宅型有料老人ホーム恩送り（定員25）</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
+          <t>公表画面の特色の欄に「有料老人ホーム併設の介護事業所であり、主に施設内での介護サービスを提供している」との記載がある</t>
         </is>
       </c>
     </row>
     <row r="80" ht="32" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
+          <t>併設</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護ステーションゆう</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>6人</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>43人</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホームゆう（介護付・定員20）及びサービス付き高齢者住宅ゆう（30戸・隣接）</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>北海道の届出済有料老人ホーム一覧と所在地が一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
           <t>併設なし</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>指定（介護予防）訪問介護ケンセイシャレバレッジ</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>10人</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>法人は住宅型有料老人ホームひがしかぐらふらわーはうす（定員18）を運営するが、訪問介護事業所とは所在地が異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>6人</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>19人</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町ホームヘルプサービスセンター</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>13人</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>49人</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>東川町社協訪問介護事業所</t>
         </is>
       </c>
-      <c r="C80" s="20" t="inlineStr">
+      <c r="C84" s="20" t="inlineStr">
         <is>
           <t>7人</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>16人</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>社会福祉協議会が運営し、居住系の住まいの併設はない</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="14" t="inlineStr">
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>併設なし</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所 ほがらか</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
+          <t>17人</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>26人</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>所在地のグレースフルひじり野は、北海道の届出済有料老人ホーム一覧及び住所地特例適用施設一覧のいずれにも掲載がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>併設7事業所</t>
-        </is>
-      </c>
-      <c r="C81" s="31" t="inlineStr">
-        <is>
-          <t>122人</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>182人</t>
-        </is>
-      </c>
-      <c r="E81" s="14" t="inlineStr">
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>併設8事業所</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="inlineStr">
+        <is>
+          <t>128人</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>225人</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F81" s="14" t="inlineStr">
-        <is>
-          <t>把握できた訪問介護員等158人の77.2％、利用者277人の65.7％を併設の事業所が占める</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="14" t="inlineStr">
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>把握できた訪問介護員等181人の70.7％、利用者346人の65.0％を併設の事業所が占める</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="14" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>併設なし4事業所</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="inlineStr">
-        <is>
-          <t>36人</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>95人</t>
-        </is>
-      </c>
-      <c r="E82" s="14" t="inlineStr">
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>併設なし5事業所</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>53人</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>121人</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F82" s="14" t="inlineStr">
-        <is>
-          <t>社会福祉協議会3事業所とケンセイシャレバレッジである</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="377" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。注6）調査未回答の8事業所は、公表画面が訪問介護員等の人数の唯一の出所である。8事業所すべてが調査の基準日（令和7年4月1日）より前からの指定であり、基準日に開設していなかったことによる未回答ではない。訪問介護事業所 桜華の指定は令和6年10月1日であり、同一法人の居宅介護支援事業所おうか（令和7年10月1日指定）とは1年の差がある。桜華は基準日に開設していた。注7）実人数に対する常勤換算の比は事業所により大きく異なる（東神楽町ホームヘルプサービスセンター6.0人／6人に対し、縁結び8.28人／31人）。兼務の多寡によるものである。訪問系の従事者数を実人数で積み上げる場合は、この点を明記のうえ用いる。注7の2）ひばりは、同一敷地に住宅型有料老人ホームひばりの森（調査回答9人）とグループホームひばり（調査回答21人）があり、訪問介護12人との重複の有無は確かめられていない。点検事項No.1と同じ構造であるが、施設票と訪問介護の数値は一致しないため転記ではない（本シート6）。注7の3）恩送りは常勤換算人数及び訪問介護員等1人当たりのサービス提供時間の欄がいずれも0であり、利用者17人・提供時間20時間との整合がとれない。記入漏れとみられるため、常勤換算は用いない。注7の4）美瑛町ホームヘルプサービスセンターは常勤の週の勤務すべき時間数が38.75時間であり、他の10事業所（40時間）と異なる。常勤換算の水準を事業所間で比べる際に留意する。注8）ケンセイシャレバレッジの所在地は、北海道の指定事業所一覧では「北二条西3丁目254番地49」、公表画面及び公表システムの位置情報付きデータでは「北2条西3丁目254番73号」であり一致しない。移転か一覧の誤りかは確認していない。注9）残る未把握は訪問介護事業所 ほがらか（東神楽町）及び指定訪問介護ステーション ゆう（東川町）の2事業所である。この2事業所の公表画面を入手すれば、訪問介護13事業所すべての訪問介護員等の人数を把握でき、「訪問系3／13事業所」という代表性の限界が完全に解消する。注10）本シート7のとおり、把握できた訪問介護員等158人のうち122人（77.2％）が、住宅型有料老人ホーム又はサービス付き高齢者向け住宅に併設された事業所に所属している。利用者277人のうち182人（65.7％）も同様である。区域内の訪問介護は、居宅で暮らす方に対する訪問よりも、居住系の住まいの入居者に対する訪問が主となっている。第4章の在宅サービスの見込量において訪問介護を「在宅」として一括して扱うと、実態と離れた読み方につながる。見込量の算定には見える化D系列の受給者数を用いるため算定そのものへの影響はないが、本文の記述では併設の割合を明記する。併設なしの4事業所は、3町の社会福祉協議会が運営する3事業所とケンセイシャレバレッジであり、訪問介護員等は36人にとどまる。</t>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>3町の社会福祉協議会3事業所、ケンセイシャレバレッジ及びほがらかである</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="455" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>注1）訪問介護3事業所のうち2事業所（花時計・フラワー）は、実人数・常勤・非常勤のすべてが調査と公表画面で一致した。介護人材実態調査の事業所票が、公表制度の「訪問介護員等の実人数」と同じ定義で記入されていることを示している。注2）シルバーハウス訪問介護事業所は公表画面が4人多い。調査の基準日（令和7年4月1日）から公表画面の記入日（令和7年11月6日）までの約7か月間の増員とみられるが、確かめたものではない。注3）採用者数・離職者数は3事業所とも一致しない組合せがある。調査は「過去1年間」、公表画面は「前年度」であり、対象期間の解釈が異なる可能性がある。代表KPI H14（採用率と離職率の差）は各年9月30日現在の在籍者数を分母とするため、いずれの値もそのままでは用いられない。注4）点検事項No.1について、公表画面はヘルパーステーションフラワー側の13人・常勤8人・非常勤5人・採用7人・離職2人が実在の値であることを裏づける。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側の介護職員数が0であることを公表データで確かめることはできない。点検事項No.1の確定には、なお提出元への確認を要する。注5）本シートにより、公表画面を集めれば訪問系の従事者数を調査に依らずに把握できることが実証された。代表KPI H13（職種別従事者数）の把握手段として、区域内の指定事業所の公表画面を継続的に取得する方法が考えられる。注6）調査未回答の10事業所は、公表画面が訪問介護員等の人数の唯一の出所である。10事業所すべてが調査の基準日（令和7年4月1日）より前からの指定であり、基準日に開設していなかったことによる未回答ではない。訪問介護事業所 桜華の指定は令和6年10月1日であり、同一法人の居宅介護支援事業所おうか（令和7年10月1日指定）とは1年の差がある。桜華は基準日に開設していた。注7）実人数に対する常勤換算の比は事業所により大きく異なる（東神楽町ホームヘルプサービスセンター6.0人／6人に対し、縁結び8.28人／31人）。兼務の多寡によるものである。訪問系の従事者数を実人数で積み上げる場合は、この点を明記のうえ用いる。注7の2）ひばりは、同一敷地に住宅型有料老人ホームひばりの森（調査回答9人）とグループホームひばり（調査回答21人）があり、訪問介護12人との重複の有無は確かめられていない。点検事項No.1と同じ構造であるが、施設票と訪問介護の数値は一致しないため転記ではない（本シート6）。注7の3）恩送りは常勤換算人数及び訪問介護員等1人当たりのサービス提供時間の欄がいずれも0であり、利用者17人・提供時間20時間との整合がとれない。記入漏れとみられるため、常勤換算は用いない。注7の4）美瑛町ホームヘルプサービスセンターは常勤の週の勤務すべき時間数が38.75時間であり、他の12事業所（40時間）と異なる。常勤換算の水準を事業所間で比べる際に留意する。注7の5）訪問介護事業所 ほがらかは、実人数の表の訪問介護員等の常勤専従が0人であるのに、うちサービス提供責任者の行は常勤専従1人となっており、公表画面の内部で整合しない。実人数17人（常勤10・非常勤7）は概要版と一致するため、実人数はそのまま用いる。注8）ケンセイシャレバレッジの所在地は、北海道の指定事業所一覧では「北二条西3丁目254番地49」、公表画面及び公表システムの位置情報付きデータでは「北2条西3丁目254番73号」であり一致しない。移転か一覧の誤りかは確認していない。注9）区域内の訪問介護13事業所すべての公表画面が揃い、訪問介護員等181人の全数を把握した。「訪問系3／13事業所」という代表性の限界は解消した。計画本文の訪問介護の人材に関する記述は、調査の回答3事業所42人ではなく、公表画面による13事業所181人を用いる。ただし公表画面の記入日は令和7年10月3日から11月7日までであり、調査の基準日（令和7年4月1日）とは時点が異なる。本文では「令和7年10〜11月時点」と明記する。注10）本シート7のとおり、把握できた訪問介護員等181人のうち128人（70.7％）が、住宅型有料老人ホーム、サービス付き高齢者向け住宅又は介護付有料老人ホームに併設された事業所に所属している。利用者346人のうち225人（65.0％）も同様である。区域内の訪問介護は、居宅で暮らす方に対する訪問よりも、居住系の住まいの入居者に対する訪問が主となっている。第4章の在宅サービスの見込量において訪問介護を「在宅」として一括して扱うと、実態と離れた読み方につながる。見込量の算定には見える化D系列の受給者数を用いるため算定そのものへの影響はないが、本文の記述では併設の割合を明記する。併設なしの5事業所は、3町の社会福祉協議会が運営する3事業所、ケンセイシャレバレッジ及びほがらかであり、訪問介護員等は53人にとどまる。注11）前年度の採用と退職を13事業所で合計すると、採用23人に対し退職28人であり、5人の減である。退職が採用を上回るのは縁結び（採用6・退職10）など5事業所である。ただし公表制度の「前年度」と調査の「過去1年間」は対象期間の解釈が異なる可能性があるため、代表KPI H14（採用率と離職率の差）にはそのまま用いない。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A89:F89"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A64:F64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
+++ b/output/第10期計画_住まいと施設の公表名簿との突合.xlsx
@@ -648,7 +648,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>北海道が公表する8つの名簿・データ（令和8年6月30日〜7月1日現在）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査の施設等票18件及び見える化システムのK系列（事業所数）と突合した。調査だけでは把握できていなかった施設が明らかになったため、計画本文に載せる供給量の数値が変わる。作成日：令和8年8月4日。</t>
+          <t>北海道が公表する8つの名簿・データ（令和8年6月30日〜7月1日現在）から区域内の施設・住まい・指定事業所を抽出し、居所変更実態調査の施設等票18件及び見える化システムのK系列（事業所数）と突合した。調査だけでは把握できていなかった施設を確認したため、計画本文に載せる供給量の数値が変わる。作成日：令和8年8月4日。</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>点検事項No.2（同一法人の小規模多機能2事業所が利用者票の36票を占め、回答が「小規模多機能がより適切」に偏っている）の構造的な背景が明らかになった。区域内の小規模多機能がすべて1法人であるため、利用者票の偏りは調査設計の問題ではなく供給構造の反映である。</t>
+          <t>点検事項No.2（同一法人の小規模多機能2事業所が利用者票の36票を占め、回答が「小規模多機能がより適切」に偏っている）の構造的な背景を確認した。区域内の小規模多機能がすべて1法人であるため、利用者票の偏りは調査設計の問題ではなく供給構造の反映である。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
